--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="839">
   <si>
     <t>task_name</t>
   </si>
@@ -2544,9 +2544,6 @@
   </si>
   <si>
     <t>Bhavani@12</t>
-  </si>
-  <si>
-    <t>bhavani+38@secmark.in</t>
   </si>
   <si>
     <t>Test QA</t>
@@ -6331,10 +6328,10 @@
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>830</v>
+        <v>693</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>352</v>
+        <v>694</v>
       </c>
       <c r="C2" s="103" t="s">
         <v>695</v>
@@ -6399,7 +6396,7 @@
         <v>481</v>
       </c>
       <c r="D2" s="94" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -6413,7 +6410,7 @@
         <v>482</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -12345,7 +12342,7 @@
         <v>760</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D2" s="30">
         <v>46150</v>
@@ -12373,7 +12370,7 @@
         <v>698</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P2" s="12" t="s">
         <v>39</v>
@@ -12408,7 +12405,7 @@
         <v>761</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D3" s="30">
         <v>46150</v>
@@ -12440,7 +12437,7 @@
         <v>698</v>
       </c>
       <c r="O3" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>39</v>
@@ -12475,7 +12472,7 @@
         <v>762</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D4" s="30">
         <v>46150</v>
@@ -12509,7 +12506,7 @@
         <v>698</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>39</v>
@@ -12544,7 +12541,7 @@
         <v>763</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D5" s="30">
         <v>46150</v>
@@ -12578,7 +12575,7 @@
         <v>698</v>
       </c>
       <c r="O5" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>39</v>
@@ -12613,7 +12610,7 @@
         <v>764</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D6" s="30">
         <v>46150</v>
@@ -12647,7 +12644,7 @@
         <v>698</v>
       </c>
       <c r="O6" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P6" s="12" t="s">
         <v>39</v>
@@ -12682,7 +12679,7 @@
         <v>765</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D7" s="30">
         <v>46150</v>
@@ -12716,7 +12713,7 @@
         <v>698</v>
       </c>
       <c r="O7" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P7" s="12" t="s">
         <v>39</v>
@@ -12751,7 +12748,7 @@
         <v>766</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D8" s="30">
         <v>46150</v>
@@ -12785,7 +12782,7 @@
         <v>698</v>
       </c>
       <c r="O8" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P8" s="12" t="s">
         <v>39</v>
@@ -12820,7 +12817,7 @@
         <v>767</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D9" s="30">
         <v>46150</v>
@@ -12854,7 +12851,7 @@
         <v>698</v>
       </c>
       <c r="O9" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>39</v>
@@ -15981,7 +15978,7 @@
         <v>153</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D2" s="30">
         <v>46150</v>
@@ -16009,7 +16006,7 @@
         <v>698</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P2" s="50" t="s">
         <v>39</v>
@@ -16047,7 +16044,7 @@
         <v>761</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D3" s="30">
         <v>46150</v>
@@ -16079,7 +16076,7 @@
         <v>698</v>
       </c>
       <c r="O3" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P3" s="50" t="s">
         <v>39</v>
@@ -16117,7 +16114,7 @@
         <v>762</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D4" s="30">
         <v>46150</v>
@@ -16151,7 +16148,7 @@
         <v>698</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P4" s="50" t="s">
         <v>39</v>
@@ -16189,7 +16186,7 @@
         <v>763</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D5" s="30">
         <v>46150</v>
@@ -16223,7 +16220,7 @@
         <v>698</v>
       </c>
       <c r="O5" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P5" s="50" t="s">
         <v>39</v>
@@ -16261,7 +16258,7 @@
         <v>764</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D6" s="30">
         <v>46150</v>
@@ -16295,7 +16292,7 @@
         <v>698</v>
       </c>
       <c r="O6" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P6" s="50" t="s">
         <v>39</v>
@@ -16333,7 +16330,7 @@
         <v>765</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D7" s="30">
         <v>46150</v>
@@ -16367,7 +16364,7 @@
         <v>698</v>
       </c>
       <c r="O7" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P7" s="50" t="s">
         <v>39</v>
@@ -16405,7 +16402,7 @@
         <v>766</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D8" s="30">
         <v>46150</v>
@@ -16439,7 +16436,7 @@
         <v>698</v>
       </c>
       <c r="O8" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P8" s="50" t="s">
         <v>39</v>
@@ -16477,7 +16474,7 @@
         <v>767</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D9" s="30">
         <v>46150</v>
@@ -16511,7 +16508,7 @@
         <v>698</v>
       </c>
       <c r="O9" s="46" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P9" s="50" t="s">
         <v>39</v>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="10" activeTab="12"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="894">
   <si>
     <t>task_name</t>
   </si>
@@ -1683,9 +1683,6 @@
     <t>Verify Complied Task for Approval Pending tasks.</t>
   </si>
   <si>
-    <t>Verify Not Complied Task for Approval Pending tasks.</t>
-  </si>
-  <si>
     <t>Verify Complied Task for Rejected tasks.</t>
   </si>
   <si>
@@ -2130,9 +2127,6 @@
     <t>Rahul@123</t>
   </si>
   <si>
-    <t>chrome</t>
-  </si>
-  <si>
     <t>export_circulars</t>
   </si>
   <si>
@@ -2616,9 +2610,6 @@
     <t>{"new_compliance_task":"New Task"}</t>
   </si>
   <si>
-    <t>bhavani+38@secmark.in</t>
-  </si>
-  <si>
     <t>bhavani+456@secmark.in</t>
   </si>
   <si>
@@ -2634,42 +2625,6 @@
     <t>special_date_validation</t>
   </si>
   <si>
-    <t>{"coowner_name":"Bhavani TT"}</t>
-  </si>
-  <si>
-    <t>Test QA</t>
-  </si>
-  <si>
-    <t>Test the Task 15-06</t>
-  </si>
-  <si>
-    <t>Test the Task_Daily_15_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Weekly_15_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Monthly_15_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Quarterly_15_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Half_yearly_15_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Yearly_15_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Fortnightly_15_06</t>
-  </si>
-  <si>
-    <t>Test CO</t>
-  </si>
-  <si>
-    <t>{"tm_user": "bhavani+01@secmark.in", "tm_pwd": "Bhavani@123", "co_user": "bhavani+38@secmark.in", "co_pwd": "Rahul@123"}</t>
-  </si>
-  <si>
     <t>{"company_name" :"Test the Company"}</t>
   </si>
   <si>
@@ -2685,9 +2640,6 @@
     <t>new_compliances_special_task</t>
   </si>
   <si>
-    <t>Test the Task 16-06</t>
-  </si>
-  <si>
     <t>mark_actionable</t>
   </si>
   <si>
@@ -2710,6 +2662,81 @@
   </si>
   <si>
     <t>{"config_normal_task_name":"Test Normal Config Task"}</t>
+  </si>
+  <si>
+    <t>Test the Task_Daily_18_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Weekly_18_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Monthly_18_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Quarterly_18_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Half_yearly_18_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Yearly_18_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Fortnightly_18_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Only_once 18-06</t>
+  </si>
+  <si>
+    <t>rahuld@secmark.in</t>
+  </si>
+  <si>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>CS member</t>
+  </si>
+  <si>
+    <t>BSE CO</t>
+  </si>
+  <si>
+    <t>Rahul Approver</t>
+  </si>
+  <si>
+    <t>Test the Task_Only_once 22-06</t>
+  </si>
+  <si>
+    <t>Test the Task_Daily_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Weekly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Monthly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Quarterly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Half_yearly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Yearly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Fortnightly_22_06</t>
+  </si>
+  <si>
+    <t>n+D5:D22</t>
+  </si>
+  <si>
+    <t>QCC</t>
+  </si>
+  <si>
+    <t>{"coowner_name":"CS member"}</t>
+  </si>
+  <si>
+    <t>{"tm_user": "rahultm@mailinator.com", "tm_pwd": "Rahul@123", "co_user": "rahuld@secmark.in", "co_pwd": "Rahul@123"}</t>
   </si>
 </sst>
 </file>
@@ -3240,7 +3267,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3571,6 +3598,13 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6458,21 +6492,21 @@
         <v>103</v>
       </c>
       <c r="D1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C2" s="103" t="s">
-        <v>691</v>
+        <v>878</v>
       </c>
       <c r="D2" s="105" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6520,7 +6554,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="118" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="70" customFormat="1" x14ac:dyDescent="0.25">
@@ -6534,7 +6568,7 @@
         <v>478</v>
       </c>
       <c r="D2" s="94" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E2" s="50"/>
     </row>
@@ -6549,7 +6583,7 @@
         <v>479</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E3" s="66"/>
     </row>
@@ -6619,7 +6653,7 @@
         <v>299</v>
       </c>
       <c r="C8" s="100" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D8" s="94" t="s">
         <v>281</v>
@@ -6686,10 +6720,10 @@
         <v>295</v>
       </c>
       <c r="B13" s="50" t="s">
+        <v>556</v>
+      </c>
+      <c r="C13" s="100" t="s">
         <v>557</v>
-      </c>
-      <c r="C13" s="100" t="s">
-        <v>558</v>
       </c>
       <c r="D13" s="94" t="s">
         <v>281</v>
@@ -6700,10 +6734,10 @@
         <v>302</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C14" s="100" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D14" s="94" t="s">
         <v>281</v>
@@ -6717,7 +6751,7 @@
         <v>473</v>
       </c>
       <c r="C15" s="100" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D15" s="94" t="s">
         <v>281</v>
@@ -6746,7 +6780,7 @@
         <v>460</v>
       </c>
       <c r="C17" s="100" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D17" s="94" t="s">
         <v>281</v>
@@ -6761,7 +6795,7 @@
         <v>461</v>
       </c>
       <c r="C18" s="100" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D18" s="94" t="s">
         <v>281</v>
@@ -6806,7 +6840,7 @@
         <v>462</v>
       </c>
       <c r="C21" s="100" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D21" s="94" t="s">
         <v>281</v>
@@ -6821,7 +6855,7 @@
         <v>457</v>
       </c>
       <c r="C22" s="100" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D22" s="94" t="s">
         <v>281</v>
@@ -6850,7 +6884,7 @@
         <v>459</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>281</v>
@@ -6864,7 +6898,7 @@
         <v>504</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D25" s="94" t="s">
         <v>281</v>
@@ -6878,7 +6912,7 @@
         <v>505</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D26" s="94" t="s">
         <v>281</v>
@@ -6994,10 +7028,10 @@
         <v>464</v>
       </c>
       <c r="B34" s="122" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C34" s="124" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D34" s="94" t="s">
         <v>281</v>
@@ -7005,19 +7039,19 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="129" t="s">
+        <v>847</v>
+      </c>
+      <c r="B35" s="129" t="s">
         <v>849</v>
       </c>
-      <c r="B35" s="129" t="s">
-        <v>851</v>
-      </c>
       <c r="C35" s="130" t="s">
+        <v>848</v>
+      </c>
+      <c r="D35" s="131" t="s">
+        <v>280</v>
+      </c>
+      <c r="E35" t="s">
         <v>850</v>
-      </c>
-      <c r="D35" s="131" t="s">
-        <v>281</v>
-      </c>
-      <c r="E35" t="s">
-        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -7074,7 +7108,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="118" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7088,7 +7122,7 @@
         <v>478</v>
       </c>
       <c r="D2" s="94" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E2" s="50"/>
     </row>
@@ -7097,13 +7131,13 @@
         <v>507</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C3" s="95" t="s">
         <v>479</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E3" s="66"/>
     </row>
@@ -7127,7 +7161,7 @@
         <v>509</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C5" s="95" t="s">
         <v>485</v>
@@ -7173,7 +7207,7 @@
         <v>299</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D8" s="94" t="s">
         <v>281</v>
@@ -7240,7 +7274,7 @@
         <v>517</v>
       </c>
       <c r="B13" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C13" s="100" t="s">
         <v>490</v>
@@ -7254,10 +7288,10 @@
         <v>518</v>
       </c>
       <c r="B14" s="75" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C14" s="95" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D14" s="94" t="s">
         <v>281</v>
@@ -7271,7 +7305,7 @@
         <v>473</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D15" s="94" t="s">
         <v>281</v>
@@ -7299,7 +7333,7 @@
         <v>460</v>
       </c>
       <c r="C17" s="114" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D17" s="94" t="s">
         <v>281</v>
@@ -7313,7 +7347,7 @@
         <v>461</v>
       </c>
       <c r="C18" s="114" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D18" s="94" t="s">
         <v>281</v>
@@ -7330,7 +7364,7 @@
         <v>495</v>
       </c>
       <c r="D19" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -7355,7 +7389,7 @@
         <v>462</v>
       </c>
       <c r="C21" s="114" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D21" s="94" t="s">
         <v>281</v>
@@ -7369,7 +7403,7 @@
         <v>459</v>
       </c>
       <c r="C22" s="91" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D22" s="94" t="s">
         <v>281</v>
@@ -7389,15 +7423,15 @@
         <v>281</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="98" t="s">
         <v>534</v>
       </c>
       <c r="B24" s="94" t="s">
         <v>538</v>
       </c>
-      <c r="C24" s="99" t="s">
-        <v>542</v>
+      <c r="C24" s="136" t="s">
+        <v>890</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>281</v>
@@ -7411,7 +7445,7 @@
         <v>539</v>
       </c>
       <c r="C25" s="99" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D25" s="94" t="s">
         <v>281</v>
@@ -7425,7 +7459,7 @@
         <v>540</v>
       </c>
       <c r="C26" s="99" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D26" s="94" t="s">
         <v>281</v>
@@ -7517,19 +7551,19 @@
     </row>
     <row r="33" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="129" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B33" s="129" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="C33" s="130" t="s">
+        <v>848</v>
+      </c>
+      <c r="D33" s="131" t="s">
+        <v>281</v>
+      </c>
+      <c r="E33" t="s">
         <v>850</v>
-      </c>
-      <c r="D33" s="131" t="s">
-        <v>281</v>
-      </c>
-      <c r="E33" t="s">
-        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -7584,10 +7618,10 @@
         <v>300</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -7615,7 +7649,7 @@
         <v>436</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -7626,10 +7660,10 @@
         <v>299</v>
       </c>
       <c r="C5" s="91" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -7637,13 +7671,13 @@
         <v>309</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -7651,13 +7685,13 @@
         <v>310</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C7" s="66" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -7665,13 +7699,13 @@
         <v>311</v>
       </c>
       <c r="B8" s="50" t="s">
+        <v>603</v>
+      </c>
+      <c r="C8" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="C8" s="66" t="s">
-        <v>605</v>
-      </c>
       <c r="D8" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="70" customFormat="1" x14ac:dyDescent="0.25">
@@ -7930,13 +7964,13 @@
         <v>304</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C2" s="91" t="s">
         <v>347</v>
       </c>
       <c r="D2" s="71" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7944,7 +7978,7 @@
         <v>305</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C3" t="s">
         <v>434</v>
@@ -7964,7 +7998,7 @@
         <v>436</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -7986,13 +8020,13 @@
         <v>312</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C6" s="48" t="s">
         <v>315</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8000,13 +8034,13 @@
         <v>313</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C7" s="66" t="s">
         <v>292</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -8014,13 +8048,13 @@
         <v>314</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -8059,7 +8093,7 @@
     </row>
     <row r="2" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B2" s="50" t="s">
         <v>129</v>
@@ -8073,10 +8107,10 @@
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C3" s="66" t="s">
         <v>433</v>
@@ -8087,10 +8121,10 @@
     </row>
     <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>433</v>
@@ -8101,10 +8135,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C5" s="50" t="s">
         <v>434</v>
@@ -8115,10 +8149,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C6" s="50" t="s">
         <v>434</v>
@@ -8129,10 +8163,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>435</v>
@@ -8143,10 +8177,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>436</v>
@@ -8157,10 +8191,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C9" s="50" t="s">
         <v>437</v>
@@ -8171,10 +8205,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C10" s="50" t="s">
         <v>437</v>
@@ -8185,10 +8219,10 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>293</v>
@@ -8199,10 +8233,10 @@
     </row>
     <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B12" s="104" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C12" s="66" t="s">
         <v>294</v>
@@ -8213,10 +8247,10 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="50" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>315</v>
@@ -8227,10 +8261,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="50" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C14" s="50" t="s">
         <v>316</v>
@@ -8275,13 +8309,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>280</v>
@@ -8289,13 +8323,13 @@
     </row>
     <row r="3" spans="1:4" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A3" s="126" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B3" s="126" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C3" s="126" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>280</v>
@@ -8303,13 +8337,13 @@
     </row>
     <row r="4" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A4" s="126" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C4" s="126" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>281</v>
@@ -8317,13 +8351,13 @@
     </row>
     <row r="5" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A5" s="126" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C5" s="126" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>281</v>
@@ -8331,13 +8365,13 @@
     </row>
     <row r="6" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A6" s="126" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C6" s="126" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D6" s="50" t="s">
         <v>281</v>
@@ -8345,13 +8379,13 @@
     </row>
     <row r="7" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A7" s="126" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C7" s="126" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D7" s="50" t="s">
         <v>281</v>
@@ -8359,13 +8393,13 @@
     </row>
     <row r="8" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A8" s="126" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C8" s="126" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D8" s="50" t="s">
         <v>281</v>
@@ -8405,38 +8439,38 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C2" t="s">
         <v>347</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C3" t="s">
         <v>347</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C4" t="s">
         <v>347</v>
@@ -8447,16 +8481,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B5" s="50" t="s">
+        <v>742</v>
+      </c>
+      <c r="C5" s="50" t="s">
         <v>744</v>
       </c>
-      <c r="C5" s="50" t="s">
-        <v>746</v>
-      </c>
       <c r="D5" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8548,35 +8582,35 @@
         <v>136</v>
       </c>
       <c r="E1" s="118" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D2" s="116" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D3" s="116" t="s">
         <v>281</v>
@@ -8585,13 +8619,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="115" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B4" s="116" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C4" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D4" s="116" t="s">
         <v>281</v>
@@ -8600,61 +8634,61 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C5" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D5" s="133" t="s">
         <v>281</v>
       </c>
       <c r="E5" s="66" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B6" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C6" t="s">
-        <v>727</v>
-      </c>
-      <c r="D6" s="133" t="s">
+        <v>725</v>
+      </c>
+      <c r="D6" s="134" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>704</v>
+      </c>
+      <c r="B7" t="s">
+        <v>705</v>
+      </c>
+      <c r="C7" t="s">
         <v>706</v>
       </c>
-      <c r="B7" t="s">
-        <v>707</v>
-      </c>
-      <c r="C7" t="s">
-        <v>708</v>
-      </c>
-      <c r="D7" s="133" t="s">
+      <c r="D7" s="134" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>704</v>
+      </c>
+      <c r="B8" t="s">
+        <v>861</v>
+      </c>
+      <c r="C8" t="s">
         <v>706</v>
       </c>
-      <c r="B8" t="s">
-        <v>877</v>
-      </c>
-      <c r="C8" t="s">
-        <v>708</v>
-      </c>
-      <c r="D8" s="133" t="s">
-        <v>280</v>
+      <c r="D8" s="134" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -8692,35 +8726,35 @@
         <v>136</v>
       </c>
       <c r="E1" s="118" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C2" s="66" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E2" s="117" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>281</v>
@@ -8729,13 +8763,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C4" s="100" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>281</v>
@@ -8744,13 +8778,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C5" s="100" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>281</v>
@@ -8759,13 +8793,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C6" s="100" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D6" s="50" t="s">
         <v>281</v>
@@ -8774,115 +8808,115 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C7" s="66" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D7" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E7" s="120" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D8" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E8" s="117" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D9" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E9" s="120" t="s">
-        <v>859</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B10" s="50" t="s">
+        <v>673</v>
+      </c>
+      <c r="C10" s="66" t="s">
         <v>674</v>
       </c>
-      <c r="C10" s="66" t="s">
-        <v>675</v>
-      </c>
       <c r="D10" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E10" s="117" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C11" s="66" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D11" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E11" s="120" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E12" s="117" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C13" s="100" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>281</v>
@@ -8891,13 +8925,13 @@
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="58" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D14" s="50" t="s">
         <v>281</v>
@@ -8906,47 +8940,47 @@
     </row>
     <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E15" s="117" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E16" s="120" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B17" s="116" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D17" s="116" t="s">
         <v>280</v>
@@ -8988,10 +9022,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C2" t="s">
         <v>347</v>
@@ -9002,10 +9036,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C3" t="s">
         <v>433</v>
@@ -9016,10 +9050,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C4" t="s">
         <v>433</v>
@@ -9030,10 +9064,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C5" t="s">
         <v>433</v>
@@ -9044,10 +9078,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C6" t="s">
         <v>433</v>
@@ -9058,13 +9092,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C7" s="112" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D7" s="71" t="s">
         <v>280</v>
@@ -9072,13 +9106,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C8" s="112" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D8" s="75" t="s">
         <v>281</v>
@@ -9193,10 +9227,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7" s="46" t="s">
         <v>133</v>
@@ -9221,7 +9255,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B9" s="46" t="s">
         <v>134</v>
@@ -9235,10 +9269,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="46" t="s">
         <v>133</v>
@@ -9249,10 +9283,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="46" t="s">
         <v>133</v>
@@ -9263,7 +9297,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B12" s="46" t="s">
         <v>134</v>
@@ -9277,7 +9311,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B13" s="46" t="s">
         <v>134</v>
@@ -9291,7 +9325,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B14" s="46" t="s">
         <v>134</v>
@@ -9305,7 +9339,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B15" s="46" t="s">
         <v>134</v>
@@ -9319,7 +9353,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B16" s="46" t="s">
         <v>134</v>
@@ -9333,7 +9367,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B17" s="46" t="s">
         <v>134</v>
@@ -9347,7 +9381,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="106" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B18" s="46" t="s">
         <v>134</v>
@@ -9361,7 +9395,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B19" s="46" t="s">
         <v>134</v>
@@ -9408,18 +9442,18 @@
         <v>136</v>
       </c>
       <c r="E1" s="56" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D2" s="94" t="s">
         <v>281</v>
@@ -9428,95 +9462,95 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D3" s="94" t="s">
         <v>281</v>
       </c>
       <c r="E3" s="66" t="s">
-        <v>871</v>
+        <v>856</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C5" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E5" s="66" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C6" s="121" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D6" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E6" s="66" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C7" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D7" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E7" s="66" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C8" s="50" t="s">
         <v>347</v>
@@ -9525,18 +9559,18 @@
         <v>281</v>
       </c>
       <c r="E8" s="66" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B9" s="50" t="s">
+        <v>676</v>
+      </c>
+      <c r="C9" t="s">
         <v>677</v>
-      </c>
-      <c r="C9" t="s">
-        <v>678</v>
       </c>
       <c r="D9" s="50" t="s">
         <v>281</v>
@@ -9545,47 +9579,47 @@
     </row>
     <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B10" s="50" t="s">
+        <v>686</v>
+      </c>
+      <c r="C10" t="s">
+        <v>685</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>281</v>
+      </c>
+      <c r="E10" s="66" t="s">
         <v>687</v>
-      </c>
-      <c r="C10" t="s">
-        <v>686</v>
-      </c>
-      <c r="D10" s="50" t="s">
-        <v>281</v>
-      </c>
-      <c r="E10" s="66" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="122" t="s">
+        <v>729</v>
+      </c>
+      <c r="B11" s="122" t="s">
+        <v>730</v>
+      </c>
+      <c r="C11" t="s">
         <v>731</v>
       </c>
-      <c r="B11" s="122" t="s">
-        <v>732</v>
-      </c>
-      <c r="C11" t="s">
-        <v>733</v>
-      </c>
       <c r="D11" s="122" t="s">
         <v>281</v>
       </c>
       <c r="E11" s="123" t="s">
-        <v>873</v>
+        <v>858</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="122" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B12" s="122" t="s">
+        <v>789</v>
+      </c>
+      <c r="C12" s="100" t="s">
         <v>791</v>
-      </c>
-      <c r="C12" s="100" t="s">
-        <v>793</v>
       </c>
       <c r="D12" s="122" t="s">
         <v>281</v>
@@ -9593,30 +9627,30 @@
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="122" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B13" s="122" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="C13" s="100" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="D13" s="122" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E13" s="66" t="s">
-        <v>884</v>
+        <v>868</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="122" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="C14" s="100" t="s">
-        <v>883</v>
+        <v>867</v>
       </c>
       <c r="D14" s="56" t="s">
         <v>280</v>
@@ -9625,19 +9659,19 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="122" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="B15" s="121" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C15" s="121" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D15" s="121" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E15" s="125" t="s">
-        <v>870</v>
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -12159,10 +12193,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>612</v>
-      </c>
-      <c r="B1" s="39" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12170,7 +12204,7 @@
         <v>93</v>
       </c>
       <c r="B2" s="108" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12178,28 +12212,28 @@
         <v>94</v>
       </c>
       <c r="B3" s="108" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B6" s="46" t="s">
         <v>89</v>
@@ -12207,10 +12241,10 @@
     </row>
     <row r="7" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12218,23 +12252,23 @@
         <v>16</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="40" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12242,15 +12276,15 @@
         <v>16</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B12" s="113" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12258,55 +12292,55 @@
         <v>91</v>
       </c>
       <c r="B13" s="113" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
+        <v>660</v>
+      </c>
+      <c r="B14" s="46" t="s">
         <v>661</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A15" s="40" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B16" s="113" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="40" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12319,74 +12353,74 @@
     </row>
     <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A25" s="41" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A27" s="41" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A29" s="41" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12453,7 +12487,7 @@
         <v>136</v>
       </c>
       <c r="F1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -12591,7 +12625,7 @@
       <c r="B10" s="51" t="s">
         <v>322</v>
       </c>
-      <c r="C10" s="74" t="s">
+      <c r="C10" s="135" t="s">
         <v>348</v>
       </c>
       <c r="D10" s="74" t="s">
@@ -12804,7 +12838,7 @@
         <v>329</v>
       </c>
       <c r="C2" s="132" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D2" s="50">
         <v>1</v>
@@ -12821,7 +12855,7 @@
         <v>318</v>
       </c>
       <c r="C3" s="132" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D3" s="50">
         <v>1</v>
@@ -12838,7 +12872,7 @@
         <v>319</v>
       </c>
       <c r="C4" s="132" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D4" s="50">
         <v>0</v>
@@ -12855,7 +12889,7 @@
         <v>148</v>
       </c>
       <c r="C5" s="132" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D5" s="50">
         <v>1</v>
@@ -13109,16 +13143,16 @@
         <v>213</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>861</v>
+        <v>882</v>
       </c>
       <c r="D2" s="30">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="E2" s="30">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -13134,13 +13168,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N2" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P2" s="12" t="s">
         <v>39</v>
@@ -13152,7 +13186,7 @@
         <v>29</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T2" s="14">
         <v>1000</v>
@@ -13161,10 +13195,10 @@
         <v>31</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13172,22 +13206,22 @@
         <v>214</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="D3" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E3" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H3" s="30">
         <v>46242</v>
@@ -13201,13 +13235,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N3" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O3" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>39</v>
@@ -13219,7 +13253,7 @@
         <v>29</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T3" s="14">
         <v>1000</v>
@@ -13228,10 +13262,10 @@
         <v>31</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13239,28 +13273,28 @@
         <v>215</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="D4" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E4" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>400</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H4" s="30">
         <v>46248</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13">
@@ -13270,13 +13304,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>39</v>
@@ -13288,7 +13322,7 @@
         <v>29</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T4" s="14">
         <v>1000</v>
@@ -13297,7 +13331,7 @@
         <v>31</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W4" s="12" t="s">
         <v>280</v>
@@ -13308,22 +13342,22 @@
         <v>216</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="D5" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E5" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>401</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H5" s="30">
         <v>46264</v>
@@ -13339,13 +13373,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O5" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>39</v>
@@ -13357,7 +13391,7 @@
         <v>29</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T5" s="14">
         <v>1000</v>
@@ -13366,7 +13400,7 @@
         <v>31</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W5" s="12" t="s">
         <v>280</v>
@@ -13377,22 +13411,22 @@
         <v>217</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="D6" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E6" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>402</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H6" s="30">
         <v>46264</v>
@@ -13408,13 +13442,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O6" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P6" s="12" t="s">
         <v>39</v>
@@ -13426,7 +13460,7 @@
         <v>29</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T6" s="14">
         <v>1000</v>
@@ -13435,7 +13469,7 @@
         <v>31</v>
       </c>
       <c r="V6" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W6" s="12" t="s">
         <v>280</v>
@@ -13446,22 +13480,22 @@
         <v>218</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="D7" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E7" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>405</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H7" s="30">
         <v>46417</v>
@@ -13477,13 +13511,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O7" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P7" s="12" t="s">
         <v>39</v>
@@ -13495,7 +13529,7 @@
         <v>29</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T7" s="14">
         <v>1000</v>
@@ -13504,7 +13538,7 @@
         <v>31</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W7" s="12" t="s">
         <v>280</v>
@@ -13515,22 +13549,22 @@
         <v>219</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>867</v>
+        <v>888</v>
       </c>
       <c r="D8" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E8" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>403</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H8" s="30">
         <v>46537</v>
@@ -13546,13 +13580,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O8" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P8" s="12" t="s">
         <v>39</v>
@@ -13564,7 +13598,7 @@
         <v>29</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T8" s="14">
         <v>1000</v>
@@ -13573,7 +13607,7 @@
         <v>31</v>
       </c>
       <c r="V8" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W8" s="12" t="s">
         <v>280</v>
@@ -13584,22 +13618,22 @@
         <v>220</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="D9" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E9" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>407</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H9" s="30">
         <v>46233</v>
@@ -13615,13 +13649,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O9" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>39</v>
@@ -13633,7 +13667,7 @@
         <v>29</v>
       </c>
       <c r="S9" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T9" s="14">
         <v>1000</v>
@@ -13642,7 +13676,7 @@
         <v>31</v>
       </c>
       <c r="V9" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W9" s="12" t="s">
         <v>280</v>
@@ -15629,7 +15663,7 @@
     </row>
     <row r="51" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="51" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B51" s="59" t="s">
         <v>404</v>
@@ -15668,7 +15702,7 @@
     </row>
     <row r="52" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="51" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B52" s="59" t="s">
         <v>341</v>
@@ -15707,7 +15741,7 @@
     </row>
     <row r="53" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="51" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B53" s="59" t="s">
         <v>406</v>
@@ -15746,7 +15780,7 @@
     </row>
     <row r="54" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="51" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B54" s="59" t="s">
         <v>342</v>
@@ -15785,7 +15819,7 @@
     </row>
     <row r="55" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="51" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B55" s="59" t="s">
         <v>343</v>
@@ -15826,7 +15860,7 @@
     </row>
     <row r="56" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="51" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B56" s="59" t="s">
         <v>344</v>
@@ -15865,7 +15899,7 @@
     </row>
     <row r="57" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="51" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B57" s="59" t="s">
         <v>345</v>
@@ -15904,13 +15938,13 @@
     </row>
     <row r="58" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="51" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B58" s="59" t="s">
         <v>346</v>
       </c>
       <c r="C58" s="61" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D58" s="30">
         <v>46017</v>
@@ -16751,10 +16785,10 @@
         <v>876</v>
       </c>
       <c r="D2" s="30">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="E2" s="30">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -16770,13 +16804,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N2" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P2" s="50" t="s">
         <v>39</v>
@@ -16785,7 +16819,7 @@
         <v>28</v>
       </c>
       <c r="R2" s="50" t="s">
-        <v>595</v>
+        <v>891</v>
       </c>
       <c r="S2" s="50" t="s">
         <v>29</v>
@@ -16800,7 +16834,7 @@
         <v>31</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>280</v>
@@ -16811,22 +16845,22 @@
         <v>246</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="D3" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E3" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H3" s="30">
         <v>46242</v>
@@ -16840,13 +16874,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N3" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O3" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P3" s="50" t="s">
         <v>39</v>
@@ -16855,13 +16889,13 @@
         <v>28</v>
       </c>
       <c r="R3" s="50" t="s">
-        <v>595</v>
+        <v>891</v>
       </c>
       <c r="S3" s="50" t="s">
         <v>29</v>
       </c>
       <c r="T3" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="U3" s="50">
         <v>1000</v>
@@ -16870,10 +16904,10 @@
         <v>31</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16881,28 +16915,28 @@
         <v>247</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="D4" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E4" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>400</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H4" s="30">
         <v>46248</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13">
@@ -16912,13 +16946,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P4" s="50" t="s">
         <v>39</v>
@@ -16927,13 +16961,13 @@
         <v>28</v>
       </c>
       <c r="R4" s="50" t="s">
-        <v>595</v>
+        <v>891</v>
       </c>
       <c r="S4" s="50" t="s">
         <v>29</v>
       </c>
       <c r="T4" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="U4" s="50">
         <v>1000</v>
@@ -16942,10 +16976,10 @@
         <v>31</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16953,22 +16987,22 @@
         <v>248</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="D5" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E5" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>401</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H5" s="30">
         <v>46264</v>
@@ -16984,13 +17018,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O5" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P5" s="50" t="s">
         <v>39</v>
@@ -16999,13 +17033,13 @@
         <v>28</v>
       </c>
       <c r="R5" s="50" t="s">
-        <v>595</v>
+        <v>891</v>
       </c>
       <c r="S5" s="50" t="s">
         <v>29</v>
       </c>
       <c r="T5" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="U5" s="50">
         <v>1000</v>
@@ -17014,10 +17048,10 @@
         <v>31</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17025,22 +17059,22 @@
         <v>249</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="D6" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E6" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>402</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H6" s="30">
         <v>46264</v>
@@ -17056,13 +17090,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O6" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P6" s="50" t="s">
         <v>39</v>
@@ -17071,13 +17105,13 @@
         <v>28</v>
       </c>
       <c r="R6" s="50" t="s">
-        <v>595</v>
+        <v>891</v>
       </c>
       <c r="S6" s="50" t="s">
         <v>29</v>
       </c>
       <c r="T6" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="U6" s="50">
         <v>1000</v>
@@ -17086,10 +17120,10 @@
         <v>31</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17097,22 +17131,22 @@
         <v>250</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="D7" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E7" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>405</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H7" s="30">
         <v>46417</v>
@@ -17128,13 +17162,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O7" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P7" s="50" t="s">
         <v>39</v>
@@ -17143,13 +17177,13 @@
         <v>28</v>
       </c>
       <c r="R7" s="50" t="s">
-        <v>595</v>
+        <v>891</v>
       </c>
       <c r="S7" s="50" t="s">
         <v>29</v>
       </c>
       <c r="T7" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="U7" s="50">
         <v>1000</v>
@@ -17158,10 +17192,10 @@
         <v>31</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17169,22 +17203,22 @@
         <v>251</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="D8" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E8" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>403</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H8" s="30">
         <v>46537</v>
@@ -17200,13 +17234,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O8" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P8" s="50" t="s">
         <v>39</v>
@@ -17215,13 +17249,13 @@
         <v>28</v>
       </c>
       <c r="R8" s="50" t="s">
-        <v>595</v>
+        <v>891</v>
       </c>
       <c r="S8" s="50" t="s">
         <v>29</v>
       </c>
       <c r="T8" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="U8" s="50">
         <v>1000</v>
@@ -17230,10 +17264,10 @@
         <v>31</v>
       </c>
       <c r="W8" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17241,22 +17275,22 @@
         <v>252</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="D9" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E9" s="30">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>407</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H9" s="30">
         <v>46233</v>
@@ -17272,13 +17306,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="46" t="s">
-        <v>694</v>
+        <v>879</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="O9" s="46" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="P9" s="50" t="s">
         <v>39</v>
@@ -17287,13 +17321,13 @@
         <v>28</v>
       </c>
       <c r="R9" s="50" t="s">
-        <v>595</v>
+        <v>891</v>
       </c>
       <c r="S9" s="50" t="s">
         <v>29</v>
       </c>
       <c r="T9" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="U9" s="50">
         <v>1000</v>
@@ -17302,10 +17336,10 @@
         <v>31</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17347,7 +17381,7 @@
       </c>
       <c r="Q10" s="50"/>
       <c r="R10" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S10" s="50" t="s">
         <v>29</v>
@@ -17409,7 +17443,7 @@
       </c>
       <c r="Q11" s="50"/>
       <c r="R11" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S11" s="50" t="s">
         <v>29</v>
@@ -17461,7 +17495,7 @@
       <c r="P12" s="50"/>
       <c r="Q12" s="50"/>
       <c r="R12" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S12" s="50"/>
       <c r="T12" s="50"/>
@@ -17513,7 +17547,7 @@
       </c>
       <c r="Q13" s="50"/>
       <c r="R13" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S13" s="50" t="s">
         <v>29</v>
@@ -17573,7 +17607,7 @@
       </c>
       <c r="Q14" s="50"/>
       <c r="R14" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S14" s="50" t="s">
         <v>29</v>
@@ -17635,7 +17669,7 @@
       </c>
       <c r="Q15" s="50"/>
       <c r="R15" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S15" s="50" t="s">
         <v>29</v>
@@ -17687,7 +17721,7 @@
       <c r="P16" s="50"/>
       <c r="Q16" s="50"/>
       <c r="R16" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S16" s="50"/>
       <c r="T16" s="50"/>
@@ -17739,7 +17773,7 @@
       </c>
       <c r="Q17" s="50"/>
       <c r="R17" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S17" s="50" t="s">
         <v>29</v>
@@ -17799,7 +17833,7 @@
       </c>
       <c r="Q18" s="50"/>
       <c r="R18" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S18" s="50" t="s">
         <v>29</v>
@@ -17851,7 +17885,7 @@
       <c r="P19" s="50"/>
       <c r="Q19" s="50"/>
       <c r="R19" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S19" s="50"/>
       <c r="T19" s="50"/>
@@ -17901,7 +17935,7 @@
       </c>
       <c r="Q20" s="50"/>
       <c r="R20" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S20" s="50" t="s">
         <v>29</v>
@@ -17963,7 +17997,7 @@
       </c>
       <c r="Q21" s="50"/>
       <c r="R21" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S21" s="50" t="s">
         <v>29</v>
@@ -18017,7 +18051,7 @@
       <c r="P22" s="50"/>
       <c r="Q22" s="50"/>
       <c r="R22" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S22" s="50"/>
       <c r="T22" s="50"/>
@@ -18067,7 +18101,7 @@
       </c>
       <c r="Q23" s="50"/>
       <c r="R23" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S23" s="50" t="s">
         <v>29</v>
@@ -18121,7 +18155,7 @@
       <c r="P24" s="50"/>
       <c r="Q24" s="50"/>
       <c r="R24" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S24" s="50"/>
       <c r="T24" s="50"/>
@@ -18173,7 +18207,7 @@
       </c>
       <c r="Q25" s="50"/>
       <c r="R25" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S25" s="50" t="s">
         <v>29</v>
@@ -18227,7 +18261,7 @@
       <c r="P26" s="50"/>
       <c r="Q26" s="50"/>
       <c r="R26" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S26" s="50"/>
       <c r="T26" s="50"/>
@@ -18277,7 +18311,7 @@
       </c>
       <c r="Q27" s="50"/>
       <c r="R27" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S27" s="50" t="s">
         <v>29</v>
@@ -18331,7 +18365,7 @@
       <c r="P28" s="50"/>
       <c r="Q28" s="50"/>
       <c r="R28" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S28" s="50"/>
       <c r="T28" s="50"/>
@@ -18381,7 +18415,7 @@
       </c>
       <c r="Q29" s="50"/>
       <c r="R29" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S29" s="50" t="s">
         <v>29</v>
@@ -18441,7 +18475,7 @@
       </c>
       <c r="Q30" s="50"/>
       <c r="R30" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S30" s="50" t="s">
         <v>29</v>
@@ -18495,7 +18529,7 @@
       <c r="P31" s="50"/>
       <c r="Q31" s="50"/>
       <c r="R31" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S31" s="50"/>
       <c r="T31" s="50"/>
@@ -18545,7 +18579,7 @@
       </c>
       <c r="Q32" s="50"/>
       <c r="R32" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S32" s="50" t="s">
         <v>29</v>
@@ -18605,7 +18639,7 @@
       </c>
       <c r="Q33" s="50"/>
       <c r="R33" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S33" s="50" t="s">
         <v>29</v>
@@ -18659,7 +18693,7 @@
       </c>
       <c r="Q34" s="50"/>
       <c r="R34" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S34" s="50"/>
       <c r="T34" s="50"/>
@@ -18709,7 +18743,7 @@
       </c>
       <c r="Q35" s="50"/>
       <c r="R35" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S35" s="50" t="s">
         <v>29</v>
@@ -18761,7 +18795,7 @@
       <c r="P36" s="50"/>
       <c r="Q36" s="50"/>
       <c r="R36" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S36" s="50"/>
       <c r="T36" s="50"/>
@@ -18809,7 +18843,7 @@
       <c r="P37" s="50"/>
       <c r="Q37" s="50"/>
       <c r="R37" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S37" s="50" t="s">
         <v>29</v>
@@ -18861,7 +18895,7 @@
       <c r="P38" s="50"/>
       <c r="Q38" s="50"/>
       <c r="R38" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S38" s="50"/>
       <c r="T38" s="50" t="s">
@@ -18911,7 +18945,7 @@
       <c r="P39" s="21"/>
       <c r="Q39" s="21"/>
       <c r="R39" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S39" s="21" t="s">
         <v>83</v>
@@ -18955,7 +18989,7 @@
       <c r="P40" s="12"/>
       <c r="Q40" s="12"/>
       <c r="R40" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S40" s="12"/>
       <c r="T40" s="12"/>
@@ -18991,7 +19025,7 @@
       <c r="P41" s="12"/>
       <c r="Q41" s="12"/>
       <c r="R41" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S41" s="12"/>
       <c r="T41" s="12"/>
@@ -19043,7 +19077,7 @@
       </c>
       <c r="Q42" s="12"/>
       <c r="R42" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S42" s="12" t="s">
         <v>29</v>
@@ -19089,7 +19123,7 @@
       <c r="P43" s="12"/>
       <c r="Q43" s="12"/>
       <c r="R43" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S43" s="12"/>
       <c r="T43" s="12" t="s">
@@ -19127,7 +19161,7 @@
       <c r="P44" s="12"/>
       <c r="Q44" s="12"/>
       <c r="R44" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S44" s="12"/>
       <c r="T44" s="14"/>
@@ -19169,7 +19203,7 @@
       <c r="P45" s="12"/>
       <c r="Q45" s="12"/>
       <c r="R45" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S45" s="12"/>
       <c r="T45" s="12"/>
@@ -19211,7 +19245,7 @@
       <c r="P46" s="12"/>
       <c r="Q46" s="12"/>
       <c r="R46" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S46" s="12"/>
       <c r="T46" s="12"/>
@@ -19253,7 +19287,7 @@
       <c r="P47" s="12"/>
       <c r="Q47" s="12"/>
       <c r="R47" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S47" s="12"/>
       <c r="T47" s="12"/>
@@ -19295,7 +19329,7 @@
       <c r="P48" s="12"/>
       <c r="Q48" s="12"/>
       <c r="R48" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S48" s="12"/>
       <c r="T48" s="12"/>
@@ -19337,7 +19371,7 @@
       <c r="P49" s="12"/>
       <c r="Q49" s="12"/>
       <c r="R49" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S49" s="12"/>
       <c r="T49" s="12"/>
@@ -19379,7 +19413,7 @@
       <c r="P50" s="12"/>
       <c r="Q50" s="12"/>
       <c r="R50" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S50" s="12"/>
       <c r="T50" s="12"/>
@@ -19421,7 +19455,7 @@
       <c r="P51" s="12"/>
       <c r="Q51" s="12"/>
       <c r="R51" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S51" s="12"/>
       <c r="T51" s="12"/>
@@ -19434,7 +19468,7 @@
     </row>
     <row r="52" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="50" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B52" s="50" t="s">
         <v>340</v>
@@ -19463,7 +19497,7 @@
       <c r="P52" s="12"/>
       <c r="Q52" s="12"/>
       <c r="R52" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S52" s="12"/>
       <c r="T52" s="12"/>
@@ -19476,7 +19510,7 @@
     </row>
     <row r="53" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="50" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B53" s="90" t="s">
         <v>341</v>
@@ -19505,7 +19539,7 @@
       <c r="P53" s="12"/>
       <c r="Q53" s="12"/>
       <c r="R53" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S53" s="12"/>
       <c r="T53" s="14"/>
@@ -19518,7 +19552,7 @@
     </row>
     <row r="54" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="50" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B54" s="50" t="s">
         <v>342</v>
@@ -19549,7 +19583,7 @@
         <v>408</v>
       </c>
       <c r="R54" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S54" s="12"/>
       <c r="T54" s="14"/>
@@ -19562,7 +19596,7 @@
     </row>
     <row r="55" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="50" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B55" s="90" t="s">
         <v>343</v>
@@ -19591,7 +19625,7 @@
       <c r="P55" s="12"/>
       <c r="Q55" s="12"/>
       <c r="R55" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S55" s="12"/>
       <c r="T55" s="14"/>
@@ -19604,7 +19638,7 @@
     </row>
     <row r="56" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="50" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B56" s="50" t="s">
         <v>344</v>
@@ -19633,7 +19667,7 @@
       <c r="P56" s="12"/>
       <c r="Q56" s="12"/>
       <c r="R56" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S56" s="12"/>
       <c r="T56" s="14"/>
@@ -19646,7 +19680,7 @@
     </row>
     <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="50" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B57" s="90" t="s">
         <v>345</v>
@@ -19675,7 +19709,7 @@
       <c r="P57" s="12"/>
       <c r="Q57" s="12"/>
       <c r="R57" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S57" s="12"/>
       <c r="T57" s="14"/>
@@ -19688,7 +19722,7 @@
     </row>
     <row r="58" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="50" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B58" s="50" t="s">
         <v>346</v>
@@ -19717,7 +19751,7 @@
       <c r="P58" s="12"/>
       <c r="Q58" s="12"/>
       <c r="R58" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S58" s="12"/>
       <c r="T58" s="12"/>
@@ -19747,7 +19781,7 @@
       <c r="P59" s="12"/>
       <c r="Q59" s="12"/>
       <c r="R59" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S59" s="12"/>
       <c r="T59" s="12"/>
@@ -20053,13 +20087,13 @@
     </row>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C2" s="66" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>280</v>
@@ -20067,27 +20101,27 @@
     </row>
     <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B3" s="56" t="s">
+        <v>835</v>
+      </c>
+      <c r="C3" s="66" t="s">
         <v>837</v>
       </c>
-      <c r="C3" s="66" t="s">
-        <v>839</v>
-      </c>
       <c r="D3" s="56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B4" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D4" t="s">
         <v>280</v>
@@ -20095,86 +20129,86 @@
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B6" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B7" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C7" s="66" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B8" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B9" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B10" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="1"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="6" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,15 @@
     <sheet name="special_dashboard_test_cases" sheetId="10" r:id="rId11"/>
     <sheet name="normal_tp_test_cases" sheetId="11" r:id="rId12"/>
     <sheet name="special_tp_test_cases" sheetId="12" r:id="rId13"/>
-    <sheet name="notifications_test_cases" sheetId="13" r:id="rId14"/>
-    <sheet name="notification_test_cases" sheetId="21" r:id="rId15"/>
-    <sheet name="compliance_history_test_cases" sheetId="20" r:id="rId16"/>
-    <sheet name="updates_test_cases" sheetId="14" r:id="rId17"/>
-    <sheet name="project_test_cases" sheetId="19" r:id="rId18"/>
-    <sheet name="normal_task_sections_test_cases" sheetId="15" r:id="rId19"/>
-    <sheet name="settings_test_cases" sheetId="17" r:id="rId20"/>
-    <sheet name="helper" sheetId="8" r:id="rId21"/>
+    <sheet name="calendar_test_cases" sheetId="24" r:id="rId14"/>
+    <sheet name="notifications_test_cases" sheetId="13" r:id="rId15"/>
+    <sheet name="notification_test_cases" sheetId="21" r:id="rId16"/>
+    <sheet name="compliance_history_test_cases" sheetId="20" r:id="rId17"/>
+    <sheet name="updates_test_cases" sheetId="14" r:id="rId18"/>
+    <sheet name="project_test_cases" sheetId="19" r:id="rId19"/>
+    <sheet name="normal_task_sections_test_cases" sheetId="15" r:id="rId20"/>
+    <sheet name="settings_test_cases" sheetId="17" r:id="rId21"/>
+    <sheet name="helper" sheetId="8" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">dashboard_test_cases!$A$1:$D$26</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="905">
   <si>
     <t>task_name</t>
   </si>
@@ -2163,9 +2164,6 @@
     <t>search_validation</t>
   </si>
   <si>
-    <t>{"user_name":"Bhavani Arrolla"}</t>
-  </si>
-  <si>
     <t>issuer_link_downloads</t>
   </si>
   <si>
@@ -2685,58 +2683,94 @@
     <t>Test the Task_Fortnightly_18_06</t>
   </si>
   <si>
-    <t>Test the Task_Only_once 18-06</t>
+    <t>edge</t>
+  </si>
+  <si>
+    <t>CS member</t>
+  </si>
+  <si>
+    <t>BSE CO</t>
+  </si>
+  <si>
+    <t>Rahul Approver</t>
+  </si>
+  <si>
+    <t>Test the Task_Daily_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Weekly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Monthly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Quarterly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Half_yearly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Yearly_22_06</t>
+  </si>
+  <si>
+    <t>Test the Task_Fortnightly_22_06</t>
+  </si>
+  <si>
+    <t>n+D5:D22</t>
+  </si>
+  <si>
+    <t>QCC</t>
+  </si>
+  <si>
+    <t>{"coowner_name":"CS member"}</t>
+  </si>
+  <si>
+    <t>{"tm_user": "rahultm@mailinator.com", "tm_pwd": "Rahul@123", "co_user": "rahuld@secmark.in", "co_pwd": "Rahul@123"}</t>
+  </si>
+  <si>
+    <t>{"user_name":"CS member"}</t>
+  </si>
+  <si>
+    <t>Test the Task_Only_once 24-06</t>
+  </si>
+  <si>
+    <t>special_column_chooser</t>
+  </si>
+  <si>
+    <t>TC_DASHBOARD_34</t>
+  </si>
+  <si>
+    <t>new_compliances_column_chooser</t>
+  </si>
+  <si>
+    <t>new_compliances_export_all_data</t>
+  </si>
+  <si>
+    <t>TC_DASHBOARD_35</t>
+  </si>
+  <si>
+    <t>calendar</t>
+  </si>
+  <si>
+    <t>TC_Calendar_1</t>
+  </si>
+  <si>
+    <t>check_day_week_month</t>
+  </si>
+  <si>
+    <t>validate_today_task</t>
+  </si>
+  <si>
+    <t>TC_Calendar_2</t>
+  </si>
+  <si>
+    <t>{"calendar_task_name":"Test Calendar Task"}</t>
   </si>
   <si>
     <t>rahuld@secmark.in</t>
   </si>
   <si>
-    <t>edge</t>
-  </si>
-  <si>
-    <t>CS member</t>
-  </si>
-  <si>
-    <t>BSE CO</t>
-  </si>
-  <si>
-    <t>Rahul Approver</t>
-  </si>
-  <si>
-    <t>Test the Task_Only_once 22-06</t>
-  </si>
-  <si>
-    <t>Test the Task_Daily_22_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Weekly_22_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Monthly_22_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Quarterly_22_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Half_yearly_22_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Yearly_22_06</t>
-  </si>
-  <si>
-    <t>Test the Task_Fortnightly_22_06</t>
-  </si>
-  <si>
-    <t>n+D5:D22</t>
-  </si>
-  <si>
-    <t>QCC</t>
-  </si>
-  <si>
-    <t>{"coowner_name":"CS member"}</t>
-  </si>
-  <si>
-    <t>{"tm_user": "rahultm@mailinator.com", "tm_pwd": "Rahul@123", "co_user": "rahuld@secmark.in", "co_pwd": "Rahul@123"}</t>
+    <t>Test the Task_Only_once 29-06</t>
   </si>
 </sst>
 </file>
@@ -3267,7 +3301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3598,7 +3632,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6041,8 +6074,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:D19" totalsRowShown="0" headerRowDxfId="124" dataDxfId="123">
-  <autoFilter ref="A1:D19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:D20" totalsRowShown="0" headerRowDxfId="124" dataDxfId="123">
+  <autoFilter ref="A1:D20"/>
   <tableColumns count="4">
     <tableColumn id="3" name="module_to_test" dataDxfId="122"/>
     <tableColumn id="4" name="execution" dataDxfId="121"/>
@@ -6497,13 +6530,13 @@
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>877</v>
+        <v>903</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>689</v>
       </c>
       <c r="C2" s="103" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="D2" s="105" t="s">
         <v>597</v>
@@ -6530,7 +6563,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -6670,7 +6703,7 @@
         <v>487</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -7028,10 +7061,10 @@
         <v>464</v>
       </c>
       <c r="B34" s="122" t="s">
+        <v>735</v>
+      </c>
+      <c r="C34" s="124" t="s">
         <v>736</v>
-      </c>
-      <c r="C34" s="124" t="s">
-        <v>737</v>
       </c>
       <c r="D34" s="94" t="s">
         <v>281</v>
@@ -7039,24 +7072,52 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="129" t="s">
+        <v>846</v>
+      </c>
+      <c r="B35" s="129" t="s">
+        <v>848</v>
+      </c>
+      <c r="C35" s="130" t="s">
         <v>847</v>
       </c>
-      <c r="B35" s="129" t="s">
+      <c r="D35" s="131" t="s">
+        <v>281</v>
+      </c>
+      <c r="E35" t="s">
         <v>849</v>
       </c>
-      <c r="C35" s="130" t="s">
-        <v>848</v>
-      </c>
-      <c r="D35" s="131" t="s">
-        <v>280</v>
-      </c>
-      <c r="E35" t="s">
-        <v>850</v>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="129" t="s">
+        <v>893</v>
+      </c>
+      <c r="B36" s="129" t="s">
+        <v>894</v>
+      </c>
+      <c r="C36" s="100" t="s">
+        <v>550</v>
+      </c>
+      <c r="D36" s="131" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="129" t="s">
+        <v>896</v>
+      </c>
+      <c r="B37" s="129" t="s">
+        <v>895</v>
+      </c>
+      <c r="C37" s="100" t="s">
+        <v>501</v>
+      </c>
+      <c r="D37" s="131" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D26"/>
-  <conditionalFormatting sqref="D2:D35">
+  <conditionalFormatting sqref="D2:D37">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7131,7 +7192,7 @@
         <v>507</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C3" s="95" t="s">
         <v>479</v>
@@ -7161,7 +7222,7 @@
         <v>509</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C5" s="95" t="s">
         <v>485</v>
@@ -7252,7 +7313,7 @@
         <v>501</v>
       </c>
       <c r="D11" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -7364,7 +7425,7 @@
         <v>495</v>
       </c>
       <c r="D19" s="94" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -7430,8 +7491,8 @@
       <c r="B24" s="94" t="s">
         <v>538</v>
       </c>
-      <c r="C24" s="136" t="s">
-        <v>890</v>
+      <c r="C24" s="135" t="s">
+        <v>886</v>
       </c>
       <c r="D24" s="94" t="s">
         <v>281</v>
@@ -7551,19 +7612,19 @@
     </row>
     <row r="33" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="129" t="s">
+        <v>846</v>
+      </c>
+      <c r="B33" s="129" t="s">
+        <v>859</v>
+      </c>
+      <c r="C33" s="130" t="s">
         <v>847</v>
       </c>
-      <c r="B33" s="129" t="s">
-        <v>860</v>
-      </c>
-      <c r="C33" s="130" t="s">
-        <v>848</v>
-      </c>
       <c r="D33" s="131" t="s">
         <v>281</v>
       </c>
       <c r="E33" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -7970,7 +8031,7 @@
         <v>347</v>
       </c>
       <c r="D2" s="71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7978,13 +8039,13 @@
         <v>305</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C3" t="s">
         <v>434</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7998,7 +8059,7 @@
         <v>436</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -8006,13 +8067,13 @@
         <v>310</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>299</v>
+        <v>892</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>293</v>
       </c>
       <c r="D5" s="71" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -8020,13 +8081,13 @@
         <v>312</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C6" s="48" t="s">
         <v>315</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -8034,13 +8095,13 @@
         <v>313</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C7" s="66" t="s">
         <v>292</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -8048,13 +8109,13 @@
         <v>314</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C8" s="66" t="s">
         <v>604</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -8067,6 +8128,72 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="118" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="118" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" s="118" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1" s="118" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="118" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
+        <v>898</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>899</v>
+      </c>
+      <c r="C2" s="91" t="s">
+        <v>347</v>
+      </c>
+      <c r="D2" s="71" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
+        <v>901</v>
+      </c>
+      <c r="B3" t="s">
+        <v>900</v>
+      </c>
+      <c r="C3" s="91" t="s">
+        <v>347</v>
+      </c>
+      <c r="D3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="117" t="s">
+        <v>902</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8282,7 +8409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8312,10 +8439,10 @@
         <v>562</v>
       </c>
       <c r="B2" s="50" t="s">
+        <v>791</v>
+      </c>
+      <c r="C2" s="50" t="s">
         <v>792</v>
-      </c>
-      <c r="C2" s="50" t="s">
-        <v>793</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>280</v>
@@ -8326,10 +8453,10 @@
         <v>563</v>
       </c>
       <c r="B3" s="126" t="s">
+        <v>793</v>
+      </c>
+      <c r="C3" s="126" t="s">
         <v>794</v>
-      </c>
-      <c r="C3" s="126" t="s">
-        <v>795</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>280</v>
@@ -8340,13 +8467,13 @@
         <v>564</v>
       </c>
       <c r="B4" s="50" t="s">
+        <v>795</v>
+      </c>
+      <c r="C4" s="126" t="s">
         <v>796</v>
       </c>
-      <c r="C4" s="126" t="s">
-        <v>797</v>
-      </c>
       <c r="D4" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
@@ -8354,13 +8481,13 @@
         <v>565</v>
       </c>
       <c r="B5" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="C5" s="126" t="s">
         <v>798</v>
       </c>
-      <c r="C5" s="126" t="s">
-        <v>799</v>
-      </c>
       <c r="D5" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
@@ -8368,13 +8495,13 @@
         <v>566</v>
       </c>
       <c r="B6" s="50" t="s">
+        <v>799</v>
+      </c>
+      <c r="C6" s="126" t="s">
         <v>800</v>
       </c>
-      <c r="C6" s="126" t="s">
-        <v>801</v>
-      </c>
       <c r="D6" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
@@ -8382,13 +8509,13 @@
         <v>567</v>
       </c>
       <c r="B7" s="50" t="s">
+        <v>801</v>
+      </c>
+      <c r="C7" s="126" t="s">
         <v>802</v>
       </c>
-      <c r="C7" s="126" t="s">
-        <v>803</v>
-      </c>
       <c r="D7" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
@@ -8396,13 +8523,13 @@
         <v>568</v>
       </c>
       <c r="B8" s="50" t="s">
+        <v>803</v>
+      </c>
+      <c r="C8" s="126" t="s">
         <v>804</v>
       </c>
-      <c r="C8" s="126" t="s">
-        <v>805</v>
-      </c>
       <c r="D8" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -8410,7 +8537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8439,10 +8566,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="50" t="s">
+        <v>716</v>
+      </c>
+      <c r="B2" s="50" t="s">
         <v>717</v>
-      </c>
-      <c r="B2" s="50" t="s">
-        <v>718</v>
       </c>
       <c r="C2" t="s">
         <v>347</v>
@@ -8453,10 +8580,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C3" t="s">
         <v>347</v>
@@ -8467,10 +8594,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C4" t="s">
         <v>347</v>
@@ -8481,13 +8608,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
+        <v>742</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>741</v>
+      </c>
+      <c r="C5" s="50" t="s">
         <v>743</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>742</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>744</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>281</v>
@@ -8556,7 +8683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8593,13 +8720,13 @@
         <v>586</v>
       </c>
       <c r="C2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D2" s="116" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>702</v>
+        <v>890</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -8610,10 +8737,10 @@
         <v>631</v>
       </c>
       <c r="C3" t="s">
-        <v>739</v>
-      </c>
-      <c r="D3" s="116" t="s">
-        <v>281</v>
+        <v>738</v>
+      </c>
+      <c r="D3" s="133" t="s">
+        <v>280</v>
       </c>
       <c r="E3" s="66"/>
     </row>
@@ -8622,12 +8749,12 @@
         <v>583</v>
       </c>
       <c r="B4" s="116" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C4" t="s">
-        <v>740</v>
-      </c>
-      <c r="D4" s="116" t="s">
+        <v>739</v>
+      </c>
+      <c r="D4" s="133" t="s">
         <v>281</v>
       </c>
       <c r="E4" s="66"/>
@@ -8640,13 +8767,13 @@
         <v>587</v>
       </c>
       <c r="C5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D5" s="133" t="s">
         <v>281</v>
       </c>
       <c r="E5" s="66" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8657,37 +8784,37 @@
         <v>690</v>
       </c>
       <c r="C6" t="s">
-        <v>725</v>
-      </c>
-      <c r="D6" s="134" t="s">
+        <v>724</v>
+      </c>
+      <c r="D6" s="133" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>703</v>
+      </c>
+      <c r="B7" t="s">
         <v>704</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>705</v>
       </c>
-      <c r="C7" t="s">
-        <v>706</v>
-      </c>
-      <c r="D7" s="134" t="s">
+      <c r="D7" s="133" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C8" t="s">
-        <v>706</v>
-      </c>
-      <c r="D8" s="134" t="s">
+        <v>705</v>
+      </c>
+      <c r="D8" s="133" t="s">
         <v>281</v>
       </c>
     </row>
@@ -8700,7 +8827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8743,7 +8870,7 @@
         <v>281</v>
       </c>
       <c r="E2" s="117" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -8754,7 +8881,7 @@
         <v>603</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>281</v>
@@ -8766,7 +8893,7 @@
         <v>627</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C4" s="100" t="s">
         <v>550</v>
@@ -8781,10 +8908,10 @@
         <v>637</v>
       </c>
       <c r="B5" s="50" t="s">
+        <v>746</v>
+      </c>
+      <c r="C5" s="100" t="s">
         <v>747</v>
-      </c>
-      <c r="C5" s="100" t="s">
-        <v>748</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>281</v>
@@ -8796,7 +8923,7 @@
         <v>638</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C6" s="100" t="s">
         <v>557</v>
@@ -8808,7 +8935,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B7" s="50" t="s">
         <v>684</v>
@@ -8820,12 +8947,12 @@
         <v>281</v>
       </c>
       <c r="E7" s="120" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B8" s="50" t="s">
         <v>683</v>
@@ -8837,12 +8964,12 @@
         <v>281</v>
       </c>
       <c r="E8" s="117" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B9" s="50" t="s">
         <v>651</v>
@@ -8854,12 +8981,12 @@
         <v>281</v>
       </c>
       <c r="E9" s="120" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>673</v>
@@ -8868,18 +8995,18 @@
         <v>674</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E10" s="117" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C11" s="66" t="s">
         <v>629</v>
@@ -8888,12 +9015,12 @@
         <v>281</v>
       </c>
       <c r="E11" s="120" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B12" s="50" t="s">
         <v>626</v>
@@ -8902,21 +9029,21 @@
         <v>628</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E12" s="117" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B13" s="50" t="s">
+        <v>781</v>
+      </c>
+      <c r="C13" s="100" t="s">
         <v>782</v>
-      </c>
-      <c r="C13" s="100" t="s">
-        <v>783</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>281</v>
@@ -8925,10 +9052,10 @@
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="58" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C14" s="66" t="s">
         <v>628</v>
@@ -8940,7 +9067,7 @@
     </row>
     <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B15" s="50" t="s">
         <v>640</v>
@@ -8949,15 +9076,15 @@
         <v>628</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E15" s="117" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B16" s="50" t="s">
         <v>641</v>
@@ -8966,15 +9093,15 @@
         <v>628</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E16" s="120" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B17" s="116" t="s">
         <v>639</v>
@@ -8983,7 +9110,7 @@
         <v>628</v>
       </c>
       <c r="D17" s="116" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E17" s="75"/>
     </row>
@@ -8995,7 +9122,311 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="17.25" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.5703125" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="41" t="s">
+        <v>811</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>545</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="41" t="s">
+        <v>559</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="41" t="s">
+        <v>558</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
+        <v>897</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>560</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="41" t="s">
+        <v>718</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>561</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
+        <v>593</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="41" t="s">
+        <v>615</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
+        <v>623</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="106" t="s">
+        <v>610</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="107" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="107" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="41" t="s">
+        <v>808</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="127" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="127" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9126,297 +9557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="17.25" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.5703125" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="41"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" s="41" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
-        <v>812</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>545</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
-        <v>559</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
-        <v>558</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
-        <v>560</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
-        <v>719</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
-        <v>561</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
-        <v>593</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D15" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="41" t="s">
-        <v>615</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D16" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
-        <v>623</v>
-      </c>
-      <c r="B17" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" s="46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="106" t="s">
-        <v>610</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="107" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" s="107" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="41" t="s">
-        <v>809</v>
-      </c>
-      <c r="B19" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="127" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" s="127" t="s">
-        <v>134</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9453,7 +9594,7 @@
         <v>576</v>
       </c>
       <c r="C2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D2" s="94" t="s">
         <v>281</v>
@@ -9468,13 +9609,13 @@
         <v>608</v>
       </c>
       <c r="C3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D3" s="94" t="s">
         <v>281</v>
       </c>
       <c r="E3" s="66" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9485,13 +9626,13 @@
         <v>616</v>
       </c>
       <c r="C4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -9502,13 +9643,13 @@
         <v>619</v>
       </c>
       <c r="C5" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E5" s="66" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="90" x14ac:dyDescent="0.25">
@@ -9519,13 +9660,13 @@
         <v>620</v>
       </c>
       <c r="C6" s="121" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D6" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E6" s="66" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -9536,13 +9677,13 @@
         <v>622</v>
       </c>
       <c r="C7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D7" s="50" t="s">
         <v>281</v>
       </c>
       <c r="E7" s="66" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -9559,12 +9700,12 @@
         <v>281</v>
       </c>
       <c r="E8" s="66" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B9" s="50" t="s">
         <v>676</v>
@@ -9579,7 +9720,7 @@
     </row>
     <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>686</v>
@@ -9596,30 +9737,30 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="122" t="s">
+        <v>728</v>
+      </c>
+      <c r="B11" s="122" t="s">
         <v>729</v>
       </c>
-      <c r="B11" s="122" t="s">
+      <c r="C11" t="s">
         <v>730</v>
       </c>
-      <c r="C11" t="s">
-        <v>731</v>
-      </c>
       <c r="D11" s="122" t="s">
         <v>281</v>
       </c>
       <c r="E11" s="123" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="122" t="s">
+        <v>789</v>
+      </c>
+      <c r="B12" s="122" t="s">
+        <v>788</v>
+      </c>
+      <c r="C12" s="100" t="s">
         <v>790</v>
-      </c>
-      <c r="B12" s="122" t="s">
-        <v>789</v>
-      </c>
-      <c r="C12" s="100" t="s">
-        <v>791</v>
       </c>
       <c r="D12" s="122" t="s">
         <v>281</v>
@@ -9627,30 +9768,30 @@
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="122" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B13" s="122" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C13" s="100" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D13" s="122" t="s">
         <v>280</v>
       </c>
       <c r="E13" s="66" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="122" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C14" s="100" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D14" s="56" t="s">
         <v>280</v>
@@ -9659,19 +9800,19 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="122" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B15" s="121" t="s">
+        <v>805</v>
+      </c>
+      <c r="C15" s="121" t="s">
         <v>806</v>
-      </c>
-      <c r="C15" s="121" t="s">
-        <v>807</v>
       </c>
       <c r="D15" s="121" t="s">
         <v>280</v>
       </c>
       <c r="E15" s="125" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -9683,7 +9824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -12356,7 +12497,7 @@
         <v>646</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12380,7 +12521,7 @@
         <v>648</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12388,7 +12529,7 @@
         <v>649</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -12625,7 +12766,7 @@
       <c r="B10" s="51" t="s">
         <v>322</v>
       </c>
-      <c r="C10" s="135" t="s">
+      <c r="C10" s="134" t="s">
         <v>348</v>
       </c>
       <c r="D10" s="74" t="s">
@@ -12838,7 +12979,7 @@
         <v>329</v>
       </c>
       <c r="C2" s="132" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D2" s="50">
         <v>1</v>
@@ -12855,7 +12996,7 @@
         <v>318</v>
       </c>
       <c r="C3" s="132" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D3" s="50">
         <v>1</v>
@@ -12872,7 +13013,7 @@
         <v>319</v>
       </c>
       <c r="C4" s="132" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D4" s="50">
         <v>0</v>
@@ -12889,7 +13030,7 @@
         <v>148</v>
       </c>
       <c r="C5" s="132" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D5" s="50">
         <v>1</v>
@@ -13143,16 +13284,16 @@
         <v>213</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="D2" s="30">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="E2" s="30">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -13168,13 +13309,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N2" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P2" s="12" t="s">
         <v>39</v>
@@ -13206,22 +13347,22 @@
         <v>214</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D3" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="E3" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H3" s="30">
         <v>46242</v>
@@ -13235,13 +13376,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N3" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O3" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>39</v>
@@ -13265,7 +13406,7 @@
         <v>655</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13273,28 +13414,28 @@
         <v>215</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="D4" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="E4" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>400</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H4" s="30">
         <v>46248</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13">
@@ -13304,13 +13445,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>39</v>
@@ -13334,7 +13475,7 @@
         <v>655</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13342,22 +13483,22 @@
         <v>216</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="D5" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="E5" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>401</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H5" s="30">
         <v>46264</v>
@@ -13373,13 +13514,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O5" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>39</v>
@@ -13403,7 +13544,7 @@
         <v>655</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13411,22 +13552,22 @@
         <v>217</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="D6" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="E6" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>402</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H6" s="30">
         <v>46264</v>
@@ -13442,13 +13583,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O6" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P6" s="12" t="s">
         <v>39</v>
@@ -13472,7 +13613,7 @@
         <v>655</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13480,22 +13621,22 @@
         <v>218</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D7" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="E7" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>405</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H7" s="30">
         <v>46417</v>
@@ -13511,13 +13652,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O7" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P7" s="12" t="s">
         <v>39</v>
@@ -13541,7 +13682,7 @@
         <v>655</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13549,22 +13690,22 @@
         <v>219</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D8" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="E8" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>403</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H8" s="30">
         <v>46537</v>
@@ -13580,13 +13721,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O8" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P8" s="12" t="s">
         <v>39</v>
@@ -13610,7 +13751,7 @@
         <v>655</v>
       </c>
       <c r="W8" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13618,22 +13759,22 @@
         <v>220</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D9" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="E9" s="30">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>407</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H9" s="30">
         <v>46233</v>
@@ -13649,13 +13790,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O9" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>39</v>
@@ -13679,7 +13820,7 @@
         <v>655</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13823,7 +13964,7 @@
       <c r="J12" s="12"/>
       <c r="K12" s="13"/>
       <c r="L12" s="14"/>
-      <c r="M12" s="12"/>
+      <c r="M12" s="13"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
@@ -15663,7 +15804,7 @@
     </row>
     <row r="51" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="51" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B51" s="59" t="s">
         <v>404</v>
@@ -15702,7 +15843,7 @@
     </row>
     <row r="52" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="51" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B52" s="59" t="s">
         <v>341</v>
@@ -15741,7 +15882,7 @@
     </row>
     <row r="53" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="51" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B53" s="59" t="s">
         <v>406</v>
@@ -15780,7 +15921,7 @@
     </row>
     <row r="54" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="51" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B54" s="59" t="s">
         <v>342</v>
@@ -15819,7 +15960,7 @@
     </row>
     <row r="55" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="51" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B55" s="59" t="s">
         <v>343</v>
@@ -15860,7 +16001,7 @@
     </row>
     <row r="56" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="51" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B56" s="59" t="s">
         <v>344</v>
@@ -15899,7 +16040,7 @@
     </row>
     <row r="57" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="51" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B57" s="59" t="s">
         <v>345</v>
@@ -15938,7 +16079,7 @@
     </row>
     <row r="58" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="51" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B58" s="59" t="s">
         <v>346</v>
@@ -16782,13 +16923,13 @@
         <v>150</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>876</v>
+        <v>904</v>
       </c>
       <c r="D2" s="30">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="E2" s="30">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -16804,13 +16945,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N2" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O2" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P2" s="50" t="s">
         <v>39</v>
@@ -16819,7 +16960,7 @@
         <v>28</v>
       </c>
       <c r="R2" s="50" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="S2" s="50" t="s">
         <v>29</v>
@@ -16845,22 +16986,22 @@
         <v>246</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D3" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E3" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H3" s="30">
         <v>46242</v>
@@ -16874,13 +17015,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N3" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O3" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P3" s="50" t="s">
         <v>39</v>
@@ -16889,7 +17030,7 @@
         <v>28</v>
       </c>
       <c r="R3" s="50" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="S3" s="50" t="s">
         <v>29</v>
@@ -16907,7 +17048,7 @@
         <v>655</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16915,28 +17056,28 @@
         <v>247</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D4" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E4" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>400</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H4" s="30">
         <v>46248</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13">
@@ -16946,13 +17087,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O4" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P4" s="50" t="s">
         <v>39</v>
@@ -16961,7 +17102,7 @@
         <v>28</v>
       </c>
       <c r="R4" s="50" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="S4" s="50" t="s">
         <v>29</v>
@@ -16979,7 +17120,7 @@
         <v>655</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16987,22 +17128,22 @@
         <v>248</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D5" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E5" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>401</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H5" s="30">
         <v>46264</v>
@@ -17018,13 +17159,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O5" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P5" s="50" t="s">
         <v>39</v>
@@ -17033,7 +17174,7 @@
         <v>28</v>
       </c>
       <c r="R5" s="50" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="S5" s="50" t="s">
         <v>29</v>
@@ -17051,7 +17192,7 @@
         <v>655</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17059,22 +17200,22 @@
         <v>249</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D6" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E6" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>402</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H6" s="30">
         <v>46264</v>
@@ -17090,13 +17231,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O6" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P6" s="50" t="s">
         <v>39</v>
@@ -17105,7 +17246,7 @@
         <v>28</v>
       </c>
       <c r="R6" s="50" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="S6" s="50" t="s">
         <v>29</v>
@@ -17123,7 +17264,7 @@
         <v>655</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17131,22 +17272,22 @@
         <v>250</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D7" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E7" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>405</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H7" s="30">
         <v>46417</v>
@@ -17162,13 +17303,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O7" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P7" s="50" t="s">
         <v>39</v>
@@ -17177,7 +17318,7 @@
         <v>28</v>
       </c>
       <c r="R7" s="50" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="S7" s="50" t="s">
         <v>29</v>
@@ -17195,7 +17336,7 @@
         <v>655</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17203,22 +17344,22 @@
         <v>251</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D8" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E8" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>403</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H8" s="30">
         <v>46537</v>
@@ -17234,13 +17375,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O8" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P8" s="50" t="s">
         <v>39</v>
@@ -17249,7 +17390,7 @@
         <v>28</v>
       </c>
       <c r="R8" s="50" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="S8" s="50" t="s">
         <v>29</v>
@@ -17267,7 +17408,7 @@
         <v>655</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -17275,22 +17416,22 @@
         <v>252</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D9" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E9" s="30">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>407</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H9" s="30">
         <v>46233</v>
@@ -17306,13 +17447,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="O9" s="46" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="P9" s="50" t="s">
         <v>39</v>
@@ -17321,7 +17462,7 @@
         <v>28</v>
       </c>
       <c r="R9" s="50" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="S9" s="50" t="s">
         <v>29</v>
@@ -17339,7 +17480,7 @@
         <v>655</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -19468,7 +19609,7 @@
     </row>
     <row r="52" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="50" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B52" s="50" t="s">
         <v>340</v>
@@ -19510,7 +19651,7 @@
     </row>
     <row r="53" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="50" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B53" s="90" t="s">
         <v>341</v>
@@ -19552,7 +19693,7 @@
     </row>
     <row r="54" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="50" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B54" s="50" t="s">
         <v>342</v>
@@ -19596,7 +19737,7 @@
     </row>
     <row r="55" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="50" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B55" s="90" t="s">
         <v>343</v>
@@ -19638,7 +19779,7 @@
     </row>
     <row r="56" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="50" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B56" s="50" t="s">
         <v>344</v>
@@ -19680,7 +19821,7 @@
     </row>
     <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="50" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B57" s="90" t="s">
         <v>345</v>
@@ -19722,7 +19863,7 @@
     </row>
     <row r="58" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="50" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B58" s="50" t="s">
         <v>346</v>
@@ -20087,27 +20228,27 @@
     </row>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
+        <v>812</v>
+      </c>
+      <c r="B2" s="50" t="s">
         <v>813</v>
       </c>
-      <c r="B2" s="50" t="s">
-        <v>814</v>
-      </c>
       <c r="C2" s="66" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D3" s="56" t="s">
         <v>280</v>
@@ -20115,100 +20256,100 @@
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B6" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B7" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C7" s="66" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B8" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B10" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="6" activeTab="9"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="8" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="913">
   <si>
     <t>task_name</t>
   </si>
@@ -2771,6 +2771,30 @@
   </si>
   <si>
     <t>Test the Task_Only_once 29-06</t>
+  </si>
+  <si>
+    <t>bulk_task_creation</t>
+  </si>
+  <si>
+    <t>Verify bulk task creation using Excel file upload</t>
+  </si>
+  <si>
+    <t>TC_DASHBOARD_36</t>
+  </si>
+  <si>
+    <t>TC_DASHBOARD_37</t>
+  </si>
+  <si>
+    <t>{"bulk_task_name": "Check Bulk Creation"}</t>
+  </si>
+  <si>
+    <t>{"bulk_task_name": "Test Bulk Creation"}</t>
+  </si>
+  <si>
+    <t>TC_SP_DASHBOARD_32</t>
+  </si>
+  <si>
+    <t>TC_SP_DASHBOARD_33</t>
   </si>
 </sst>
 </file>
@@ -6205,8 +6229,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:D27" totalsRowShown="0" headerRowDxfId="73" dataDxfId="71" headerRowBorderDxfId="72" tableBorderDxfId="70" totalsRowBorderDxfId="69">
-  <autoFilter ref="A1:D27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:D28" totalsRowShown="0" headerRowDxfId="73" dataDxfId="71" headerRowBorderDxfId="72" tableBorderDxfId="70" totalsRowBorderDxfId="69">
+  <autoFilter ref="A1:D28"/>
   <tableColumns count="4">
     <tableColumn id="1" name="test_case_id" dataDxfId="68"/>
     <tableColumn id="2" name="module_name" dataDxfId="67"/>
@@ -6563,7 +6587,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -6601,7 +6625,7 @@
         <v>478</v>
       </c>
       <c r="D2" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E2" s="50"/>
     </row>
@@ -6616,7 +6640,7 @@
         <v>479</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E3" s="66"/>
     </row>
@@ -6631,7 +6655,7 @@
         <v>482</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E4" s="66"/>
     </row>
@@ -6646,7 +6670,7 @@
         <v>485</v>
       </c>
       <c r="D5" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" s="66"/>
     </row>
@@ -6661,7 +6685,7 @@
         <v>474</v>
       </c>
       <c r="D6" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6675,7 +6699,7 @@
         <v>502</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6689,7 +6713,7 @@
         <v>550</v>
       </c>
       <c r="D8" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6717,7 +6741,7 @@
         <v>489</v>
       </c>
       <c r="D10" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6731,7 +6755,7 @@
         <v>501</v>
       </c>
       <c r="D11" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -6745,7 +6769,7 @@
         <v>298</v>
       </c>
       <c r="D12" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6759,7 +6783,7 @@
         <v>557</v>
       </c>
       <c r="D13" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -6773,7 +6797,7 @@
         <v>554</v>
       </c>
       <c r="D14" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6787,7 +6811,7 @@
         <v>551</v>
       </c>
       <c r="D15" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F15" s="94"/>
     </row>
@@ -6802,7 +6826,7 @@
         <v>491</v>
       </c>
       <c r="D16" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="70" customFormat="1" x14ac:dyDescent="0.25">
@@ -6816,7 +6840,7 @@
         <v>546</v>
       </c>
       <c r="D17" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E17"/>
     </row>
@@ -6831,7 +6855,7 @@
         <v>547</v>
       </c>
       <c r="D18" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E18"/>
     </row>
@@ -6846,7 +6870,7 @@
         <v>495</v>
       </c>
       <c r="D19" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E19"/>
     </row>
@@ -6861,7 +6885,7 @@
         <v>499</v>
       </c>
       <c r="D20" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E20"/>
     </row>
@@ -6876,7 +6900,7 @@
         <v>549</v>
       </c>
       <c r="D21" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E21"/>
     </row>
@@ -6891,7 +6915,7 @@
         <v>548</v>
       </c>
       <c r="D22" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E22"/>
     </row>
@@ -6906,7 +6930,7 @@
         <v>503</v>
       </c>
       <c r="D23" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -6920,7 +6944,7 @@
         <v>552</v>
       </c>
       <c r="D24" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -6934,7 +6958,7 @@
         <v>553</v>
       </c>
       <c r="D25" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -6948,7 +6972,7 @@
         <v>544</v>
       </c>
       <c r="D26" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="70" customFormat="1" x14ac:dyDescent="0.25">
@@ -7056,68 +7080,85 @@
       </c>
       <c r="E33"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="50" t="s">
-        <v>464</v>
+        <v>846</v>
       </c>
       <c r="B34" s="122" t="s">
+        <v>905</v>
+      </c>
+      <c r="C34" t="s">
+        <v>906</v>
+      </c>
+      <c r="D34" s="94" t="s">
+        <v>280</v>
+      </c>
+      <c r="E34" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="50" t="s">
+        <v>893</v>
+      </c>
+      <c r="B35" s="122" t="s">
         <v>735</v>
       </c>
-      <c r="C34" s="124" t="s">
+      <c r="C35" s="124" t="s">
         <v>736</v>
       </c>
-      <c r="D34" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="129" t="s">
-        <v>846</v>
-      </c>
-      <c r="B35" s="129" t="s">
+      <c r="D35" s="94" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="50" t="s">
+        <v>896</v>
+      </c>
+      <c r="B36" s="129" t="s">
         <v>848</v>
       </c>
-      <c r="C35" s="130" t="s">
+      <c r="C36" s="130" t="s">
         <v>847</v>
       </c>
-      <c r="D35" s="131" t="s">
-        <v>281</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="D36" s="131" t="s">
+        <v>280</v>
+      </c>
+      <c r="E36" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="129" t="s">
-        <v>893</v>
-      </c>
-      <c r="B36" s="129" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="50" t="s">
+        <v>907</v>
+      </c>
+      <c r="B37" s="129" t="s">
         <v>894</v>
       </c>
-      <c r="C36" s="100" t="s">
+      <c r="C37" s="100" t="s">
         <v>550</v>
       </c>
-      <c r="D36" s="131" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="129" t="s">
-        <v>896</v>
-      </c>
-      <c r="B37" s="129" t="s">
+      <c r="D37" s="131" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="50" t="s">
+        <v>908</v>
+      </c>
+      <c r="B38" s="129" t="s">
         <v>895</v>
       </c>
-      <c r="C37" s="100" t="s">
+      <c r="C38" s="100" t="s">
         <v>501</v>
       </c>
-      <c r="D37" s="131" t="s">
-        <v>281</v>
+      <c r="D38" s="131" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D26"/>
-  <conditionalFormatting sqref="D2:D37">
+  <conditionalFormatting sqref="D2:D38">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7144,7 +7185,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" style="70" customWidth="1"/>
@@ -7183,7 +7224,7 @@
         <v>478</v>
       </c>
       <c r="D2" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E2" s="50"/>
     </row>
@@ -7198,7 +7239,7 @@
         <v>479</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E3" s="66"/>
     </row>
@@ -7213,7 +7254,7 @@
         <v>482</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E4" s="66"/>
     </row>
@@ -7228,7 +7269,7 @@
         <v>485</v>
       </c>
       <c r="D5" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" s="66"/>
     </row>
@@ -7243,7 +7284,7 @@
         <v>474</v>
       </c>
       <c r="D6" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7257,7 +7298,7 @@
         <v>502</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -7271,7 +7312,7 @@
         <v>550</v>
       </c>
       <c r="D8" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7285,7 +7326,7 @@
         <v>487</v>
       </c>
       <c r="D9" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7299,7 +7340,7 @@
         <v>489</v>
       </c>
       <c r="D10" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7327,7 +7368,7 @@
         <v>298</v>
       </c>
       <c r="D12" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7341,7 +7382,7 @@
         <v>490</v>
       </c>
       <c r="D13" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7355,7 +7396,7 @@
         <v>554</v>
       </c>
       <c r="D14" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -7369,7 +7410,7 @@
         <v>551</v>
       </c>
       <c r="D15" s="94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -7383,12 +7424,12 @@
         <v>491</v>
       </c>
       <c r="D16" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="98" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B17" s="98" t="s">
         <v>460</v>
@@ -7397,12 +7438,12 @@
         <v>546</v>
       </c>
       <c r="D17" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="98" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B18" s="98" t="s">
         <v>461</v>
@@ -7411,12 +7452,12 @@
         <v>547</v>
       </c>
       <c r="D18" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="98" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B19" s="98" t="s">
         <v>455</v>
@@ -7425,12 +7466,12 @@
         <v>495</v>
       </c>
       <c r="D19" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="98" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B20" s="98" t="s">
         <v>456</v>
@@ -7439,12 +7480,12 @@
         <v>499</v>
       </c>
       <c r="D20" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="98" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B21" s="98" t="s">
         <v>462</v>
@@ -7453,12 +7494,12 @@
         <v>549</v>
       </c>
       <c r="D21" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="98" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B22" s="94" t="s">
         <v>459</v>
@@ -7467,12 +7508,12 @@
         <v>552</v>
       </c>
       <c r="D22" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B23" s="94" t="s">
         <v>537</v>
@@ -7481,12 +7522,12 @@
         <v>541</v>
       </c>
       <c r="D23" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="98" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B24" s="94" t="s">
         <v>538</v>
@@ -7495,12 +7536,12 @@
         <v>886</v>
       </c>
       <c r="D24" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="98" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B25" s="94" t="s">
         <v>539</v>
@@ -7509,12 +7550,12 @@
         <v>542</v>
       </c>
       <c r="D25" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="98" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B26" s="94" t="s">
         <v>540</v>
@@ -7523,112 +7564,139 @@
         <v>543</v>
       </c>
       <c r="D26" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="98" t="s">
-        <v>521</v>
-      </c>
-      <c r="B27" s="94" t="s">
+        <v>531</v>
+      </c>
+      <c r="B27" s="122" t="s">
+        <v>905</v>
+      </c>
+      <c r="C27" t="s">
+        <v>906</v>
+      </c>
+      <c r="D27" s="94" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="98" t="s">
+        <v>532</v>
+      </c>
+      <c r="B28" s="94" t="s">
         <v>465</v>
       </c>
-      <c r="C27" s="91" t="s">
+      <c r="C28" s="91" t="s">
         <v>492</v>
       </c>
-      <c r="D27" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="98" t="s">
-        <v>523</v>
-      </c>
-      <c r="B28" s="94" t="s">
+      <c r="D28" s="94" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="98" t="s">
+        <v>533</v>
+      </c>
+      <c r="B29" s="94" t="s">
         <v>466</v>
       </c>
-      <c r="C28" s="91" t="s">
+      <c r="C29" s="91" t="s">
         <v>493</v>
       </c>
-      <c r="D28" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="98" t="s">
-        <v>525</v>
-      </c>
-      <c r="B29" s="94" t="s">
+      <c r="D29" s="94" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="98" t="s">
+        <v>534</v>
+      </c>
+      <c r="B30" s="94" t="s">
         <v>467</v>
       </c>
-      <c r="C29" s="91" t="s">
+      <c r="C30" s="91" t="s">
         <v>494</v>
       </c>
-      <c r="D29" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="98" t="s">
-        <v>527</v>
-      </c>
-      <c r="B30" s="94" t="s">
+      <c r="D30" s="94" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="98" t="s">
+        <v>535</v>
+      </c>
+      <c r="B31" s="94" t="s">
         <v>468</v>
       </c>
-      <c r="C30" s="91" t="s">
+      <c r="C31" s="91" t="s">
         <v>496</v>
       </c>
-      <c r="D30" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="98" t="s">
-        <v>529</v>
-      </c>
-      <c r="B31" s="94" t="s">
+      <c r="D31" s="94" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="98" t="s">
+        <v>536</v>
+      </c>
+      <c r="B32" s="94" t="s">
         <v>469</v>
       </c>
-      <c r="C31" s="91" t="s">
+      <c r="C32" s="91" t="s">
         <v>500</v>
       </c>
-      <c r="D31" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="98" t="s">
-        <v>531</v>
-      </c>
-      <c r="B32" s="94" t="s">
+      <c r="D32" s="94" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="98" t="s">
+        <v>911</v>
+      </c>
+      <c r="B33" s="94" t="s">
         <v>470</v>
       </c>
-      <c r="C32" s="91" t="s">
+      <c r="C33" s="91" t="s">
         <v>498</v>
       </c>
-      <c r="D32" s="94" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="129" t="s">
-        <v>846</v>
-      </c>
-      <c r="B33" s="129" t="s">
+      <c r="D33" s="94" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="98" t="s">
+        <v>912</v>
+      </c>
+      <c r="B34" s="129" t="s">
         <v>859</v>
       </c>
-      <c r="C33" s="130" t="s">
+      <c r="C34" s="130" t="s">
         <v>847</v>
       </c>
-      <c r="D33" s="131" t="s">
-        <v>281</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="D34" s="131" t="s">
+        <v>280</v>
+      </c>
+      <c r="E34" t="s">
         <v>849</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D33">
+  <conditionalFormatting sqref="D34">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D27">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -9240,13 +9308,13 @@
         <v>128</v>
       </c>
       <c r="B8" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="46" t="s">
         <v>133</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9254,13 +9322,13 @@
         <v>545</v>
       </c>
       <c r="B9" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="D9" s="46" t="s">
         <v>133</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13290,10 +13358,10 @@
         <v>891</v>
       </c>
       <c r="D2" s="30">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="E2" s="30">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -16926,10 +16994,10 @@
         <v>904</v>
       </c>
       <c r="D2" s="30">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="E2" s="30">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -16992,10 +17060,10 @@
         <v>868</v>
       </c>
       <c r="D3" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="E3" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>25</v>
@@ -17062,10 +17130,10 @@
         <v>869</v>
       </c>
       <c r="D4" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="E4" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>400</v>
@@ -17134,10 +17202,10 @@
         <v>870</v>
       </c>
       <c r="D5" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="E5" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>401</v>
@@ -17206,10 +17274,10 @@
         <v>871</v>
       </c>
       <c r="D6" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="E6" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>402</v>
@@ -17278,10 +17346,10 @@
         <v>872</v>
       </c>
       <c r="D7" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="E7" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>405</v>
@@ -17350,10 +17418,10 @@
         <v>873</v>
       </c>
       <c r="D8" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="E8" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>403</v>
@@ -17422,10 +17490,10 @@
         <v>874</v>
       </c>
       <c r="D9" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="E9" s="30">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>407</v>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="8" activeTab="9"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="6" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2836" uniqueCount="933">
   <si>
     <t>task_name</t>
   </si>
@@ -1891,9 +1891,6 @@
     <t>TC_Settings_3</t>
   </si>
   <si>
-    <t>not_applicable_tasks</t>
-  </si>
-  <si>
     <t>project</t>
   </si>
   <si>
@@ -2251,9 +2248,6 @@
     <t>TC_compliance_history_4</t>
   </si>
   <si>
-    <t>Verify that all available filter options in the View column can be selected.</t>
-  </si>
-  <si>
     <t>project_column_chooser</t>
   </si>
   <si>
@@ -2581,9 +2575,6 @@
     <t>{"company_name" :"Test the Company"}</t>
   </si>
   <si>
-    <t>{"license_name":"BSE"}</t>
-  </si>
-  <si>
     <t>{"category_name":"IT","category_desc":"Demo"}</t>
   </si>
   <si>
@@ -2819,6 +2810,51 @@
   </si>
   <si>
     <t>{"internal_deadline":"Internal Deadline"}</t>
+  </si>
+  <si>
+    <t>mark_circular_as_na</t>
+  </si>
+  <si>
+    <t>TC_Settings_15</t>
+  </si>
+  <si>
+    <t>TC_Settings_16</t>
+  </si>
+  <si>
+    <t>not_applicable_search_task</t>
+  </si>
+  <si>
+    <t>not_applicable_view</t>
+  </si>
+  <si>
+    <t>not_applicable_export_data</t>
+  </si>
+  <si>
+    <t>TC_Settings_17</t>
+  </si>
+  <si>
+    <t>erify that the selected column (Company) is displayed correctly in the task list.</t>
+  </si>
+  <si>
+    <t>erify that the selected column (Company Name) is displayed correctly in the task list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Export All Data and Selected Data </t>
+  </si>
+  <si>
+    <t>{"company_name" : "Test the Company_2099", "license_name":"BSE"}</t>
+  </si>
+  <si>
+    <t>TC_DASHBOARD_39</t>
+  </si>
+  <si>
+    <t>TC_SP_DASHBOARD_34</t>
+  </si>
+  <si>
+    <t>{"special_task":"Special_task"}</t>
+  </si>
+  <si>
+    <t>{"normal_task":"normal_task"}</t>
   </si>
 </sst>
 </file>
@@ -3368,7 +3404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3716,166 +3752,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="120">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -3953,6 +3836,271 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4429,117 +4577,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -5864,8 +5901,21 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table1113" displayName="Table1113" ref="A1:D8" totalsRowShown="0" headerRowDxfId="56" headerRowBorderDxfId="55" tableBorderDxfId="54" totalsRowBorderDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table1113" displayName="Table1113" ref="A1:D8" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:D8"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="test_case_id" dataDxfId="3"/>
+    <tableColumn id="2" name="module_name" dataDxfId="2"/>
+    <tableColumn id="3" name="test_case_description" dataDxfId="1"/>
+    <tableColumn id="4" name="test_type" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table111311" displayName="Table111311" ref="A1:D14" totalsRowShown="0" headerRowDxfId="56" headerRowBorderDxfId="55" tableBorderDxfId="54" totalsRowBorderDxfId="53">
+  <autoFilter ref="A1:D14"/>
   <tableColumns count="4">
     <tableColumn id="1" name="test_case_id" dataDxfId="52"/>
     <tableColumn id="2" name="module_name" dataDxfId="51"/>
@@ -5876,9 +5926,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table111311" displayName="Table111311" ref="A1:D14" totalsRowShown="0" headerRowDxfId="48" headerRowBorderDxfId="47" tableBorderDxfId="46" totalsRowBorderDxfId="45">
-  <autoFilter ref="A1:D14"/>
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Table11131121" displayName="Table11131121" ref="A1:D5" totalsRowShown="0" headerRowDxfId="48" headerRowBorderDxfId="47" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+  <autoFilter ref="A1:D5"/>
   <tableColumns count="4">
     <tableColumn id="1" name="test_case_id" dataDxfId="44"/>
     <tableColumn id="2" name="module_name" dataDxfId="43"/>
@@ -5889,9 +5939,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Table11131121" displayName="Table11131121" ref="A1:D5" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38" totalsRowBorderDxfId="37">
-  <autoFilter ref="A1:D5"/>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table11131114" displayName="Table11131114" ref="A1:D4" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38" totalsRowBorderDxfId="37">
+  <autoFilter ref="A1:D4"/>
   <tableColumns count="4">
     <tableColumn id="1" name="test_case_id" dataDxfId="36"/>
     <tableColumn id="2" name="module_name" dataDxfId="35"/>
@@ -5902,9 +5952,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table11131114" displayName="Table11131114" ref="A1:D4" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
-  <autoFilter ref="A1:D4"/>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Table1113111420" displayName="Table1113111420" ref="A1:D17" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+  <autoFilter ref="A1:D17"/>
   <tableColumns count="4">
     <tableColumn id="1" name="test_case_id" dataDxfId="28"/>
     <tableColumn id="2" name="module_name" dataDxfId="27"/>
@@ -5915,9 +5965,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Table1113111420" displayName="Table1113111420" ref="A1:D17" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22" totalsRowBorderDxfId="21">
-  <autoFilter ref="A1:D17"/>
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Table1113111415" displayName="Table1113111415" ref="A1:D6" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+  <autoFilter ref="A1:D6"/>
   <tableColumns count="4">
     <tableColumn id="1" name="test_case_id" dataDxfId="20"/>
     <tableColumn id="2" name="module_name" dataDxfId="19"/>
@@ -5928,28 +5978,15 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Table1113111415" displayName="Table1113111415" ref="A1:D6" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:D6"/>
-  <tableColumns count="4">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Table111311141517" displayName="Table111311141517" ref="A1:E6" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:E6"/>
+  <tableColumns count="5">
     <tableColumn id="1" name="test_case_id" dataDxfId="12"/>
     <tableColumn id="2" name="module_name" dataDxfId="11"/>
     <tableColumn id="3" name="test_case_description" dataDxfId="10"/>
     <tableColumn id="4" name="test_type" dataDxfId="9"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Table111311141517" displayName="Table111311141517" ref="A1:E6" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E6"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="test_case_id" dataDxfId="4"/>
-    <tableColumn id="2" name="module_name" dataDxfId="3"/>
-    <tableColumn id="3" name="test_case_description" dataDxfId="2"/>
-    <tableColumn id="4" name="test_type" dataDxfId="1"/>
-    <tableColumn id="6" name="task_details" dataDxfId="0"/>
+    <tableColumn id="6" name="task_details" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6442,13 +6479,13 @@
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D2" s="93" t="s">
         <v>587</v>
@@ -6503,7 +6540,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -6647,7 +6684,7 @@
       </c>
       <c r="E9" s="62"/>
       <c r="F9" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6809,7 +6846,7 @@
       </c>
       <c r="E18" s="62"/>
       <c r="F18" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -7084,19 +7121,19 @@
     </row>
     <row r="34" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="47" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B34" s="110" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C34" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D34" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="F34" s="66" t="s">
         <v>134</v>
@@ -7104,13 +7141,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="47" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="B35" s="110" t="s">
+        <v>722</v>
+      </c>
+      <c r="C35" s="112" t="s">
         <v>723</v>
-      </c>
-      <c r="C35" s="112" t="s">
-        <v>724</v>
       </c>
       <c r="D35" s="82" t="s">
         <v>272</v>
@@ -7122,19 +7159,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="47" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C36" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D36" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E36" s="62" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F36" s="66" t="s">
         <v>134</v>
@@ -7142,10 +7179,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C37" s="88" t="s">
         <v>540</v>
@@ -7160,10 +7197,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="47" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C38" s="88" t="s">
         <v>491</v>
@@ -7178,24 +7215,43 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="47" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B39" s="115" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C39" s="140" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D39" s="116" t="s">
         <v>272</v>
       </c>
       <c r="E39" t="s">
-        <v>920</v>
-      </c>
-      <c r="F39" s="66"/>
+        <v>917</v>
+      </c>
+      <c r="F39" s="66" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F40" s="66"/>
+      <c r="A40" s="47" t="s">
+        <v>929</v>
+      </c>
+      <c r="B40" s="47" t="s">
+        <v>619</v>
+      </c>
+      <c r="C40" s="100" t="s">
+        <v>641</v>
+      </c>
+      <c r="D40" s="67" t="s">
+        <v>272</v>
+      </c>
+      <c r="E40" s="66" t="s">
+        <v>932</v>
+      </c>
+      <c r="F40" s="120" t="s">
+        <v>133</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D26"/>
@@ -7255,7 +7311,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7281,7 +7337,7 @@
         <v>497</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C3" s="83" t="s">
         <v>469</v>
@@ -7317,7 +7373,7 @@
         <v>499</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C5" s="83" t="s">
         <v>475</v>
@@ -7399,7 +7455,7 @@
       </c>
       <c r="E9" s="62"/>
       <c r="F9" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -7525,7 +7581,7 @@
       </c>
       <c r="E16" s="62"/>
       <c r="F16" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7543,7 +7599,7 @@
       </c>
       <c r="E17" s="62"/>
       <c r="F17" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -7561,7 +7617,7 @@
       </c>
       <c r="E18" s="62"/>
       <c r="F18" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -7662,7 +7718,7 @@
         <v>528</v>
       </c>
       <c r="C24" s="139" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D24" s="82" t="s">
         <v>272</v>
@@ -7713,16 +7769,16 @@
         <v>521</v>
       </c>
       <c r="B27" s="110" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C27" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D27" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E27" s="62" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="F27" s="66" t="s">
         <v>134</v>
@@ -7820,7 +7876,7 @@
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="86" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B33" s="82" t="s">
         <v>460</v>
@@ -7838,26 +7894,43 @@
     </row>
     <row r="34" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="86" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B34" s="115" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C34" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D34" s="116" t="s">
         <v>272</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="F34" s="66" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F35" s="66"/>
+    <row r="35" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="86" t="s">
+        <v>930</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>632</v>
+      </c>
+      <c r="C35" s="100" t="s">
+        <v>640</v>
+      </c>
+      <c r="D35" s="70" t="s">
+        <v>273</v>
+      </c>
+      <c r="E35" s="66" t="s">
+        <v>931</v>
+      </c>
+      <c r="F35" s="66" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F36" s="66"/>
@@ -7939,7 +8012,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -8015,7 +8088,7 @@
         <v>301</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C6" s="48" t="s">
         <v>592</v>
@@ -8377,7 +8450,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -8402,7 +8475,7 @@
         <v>297</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C3" t="s">
         <v>424</v>
@@ -8436,7 +8509,7 @@
         <v>302</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="C5" s="48" t="s">
         <v>285</v>
@@ -8453,7 +8526,7 @@
         <v>304</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C6" s="46" t="s">
         <v>307</v>
@@ -8470,7 +8543,7 @@
         <v>305</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C7" s="62" t="s">
         <v>284</v>
@@ -8487,7 +8560,7 @@
         <v>306</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C8" s="62" t="s">
         <v>594</v>
@@ -8644,18 +8717,18 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C2" s="87" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D2" s="67" t="s">
         <v>272</v>
@@ -8666,19 +8739,19 @@
     </row>
     <row r="3" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D3" t="s">
         <v>272</v>
       </c>
       <c r="E3" s="105" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="F3" s="66" t="s">
         <v>133</v>
@@ -8837,7 +8910,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -9184,7 +9257,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -9192,10 +9265,10 @@
         <v>552</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
@@ -9209,10 +9282,10 @@
         <v>553</v>
       </c>
       <c r="B3" s="113" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C3" s="113" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>272</v>
@@ -9226,10 +9299,10 @@
         <v>554</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C4" s="113" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>272</v>
@@ -9243,10 +9316,10 @@
         <v>555</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C5" s="113" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -9260,10 +9333,10 @@
         <v>556</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C6" s="113" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>272</v>
@@ -9277,10 +9350,10 @@
         <v>557</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C7" s="113" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>272</v>
@@ -9294,10 +9367,10 @@
         <v>558</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C8" s="113" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>272</v>
@@ -9355,15 +9428,15 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
+        <v>703</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>704</v>
-      </c>
-      <c r="B2" s="47" t="s">
-        <v>705</v>
       </c>
       <c r="C2" t="s">
         <v>337</v>
@@ -9377,10 +9450,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C3" t="s">
         <v>337</v>
@@ -9394,13 +9467,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C4" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>272</v>
@@ -9411,13 +9484,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>731</v>
+        <v>925</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -9465,7 +9538,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -9476,13 +9549,13 @@
         <v>576</v>
       </c>
       <c r="C2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D2" s="104" t="s">
         <v>272</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="F2" s="66" t="s">
         <v>134</v>
@@ -9493,10 +9566,10 @@
         <v>572</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D3" s="118" t="s">
         <v>272</v>
@@ -9511,10 +9584,10 @@
         <v>573</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D4" s="118" t="s">
         <v>272</v>
@@ -9532,13 +9605,13 @@
         <v>577</v>
       </c>
       <c r="C5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D5" s="118" t="s">
         <v>272</v>
       </c>
       <c r="E5" s="62" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="F5" s="66" t="s">
         <v>133</v>
@@ -9549,10 +9622,10 @@
         <v>575</v>
       </c>
       <c r="B6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D6" s="118" t="s">
         <v>272</v>
@@ -9563,13 +9636,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>690</v>
+      </c>
+      <c r="B7" t="s">
         <v>691</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>692</v>
-      </c>
-      <c r="C7" t="s">
-        <v>693</v>
       </c>
       <c r="D7" s="118" t="s">
         <v>272</v>
@@ -9580,13 +9653,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B8" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C8" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="D8" s="118" t="s">
         <v>272</v>
@@ -9634,24 +9707,24 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>564</v>
       </c>
       <c r="C2" s="62" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E2" s="105" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F2" s="66" t="s">
         <v>134</v>
@@ -9659,13 +9732,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>593</v>
       </c>
       <c r="C3" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>272</v>
@@ -9677,10 +9750,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C4" s="88" t="s">
         <v>540</v>
@@ -9695,13 +9768,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C5" s="88" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -9713,10 +9786,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>547</v>
@@ -9731,19 +9804,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C7" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E7" s="108" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F7" s="66" t="s">
         <v>134</v>
@@ -9751,19 +9824,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E8" s="105" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="F8" s="120" t="s">
         <v>134</v>
@@ -9771,19 +9844,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E9" s="108" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="F9" s="120" t="s">
         <v>134</v>
@@ -9791,19 +9864,19 @@
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="55" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B10" s="47" t="s">
+        <v>660</v>
+      </c>
+      <c r="C10" s="62" t="s">
         <v>661</v>
-      </c>
-      <c r="C10" s="62" t="s">
-        <v>662</v>
       </c>
       <c r="D10" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E10" s="105" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="F10" s="120" t="s">
         <v>134</v>
@@ -9811,19 +9884,19 @@
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="55" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C11" s="62" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E11" s="108" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="F11" s="120" t="s">
         <v>134</v>
@@ -9831,19 +9904,19 @@
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D12" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E12" s="105" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F12" s="120" t="s">
         <v>133</v>
@@ -9851,13 +9924,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="55" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C13" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>272</v>
@@ -9869,13 +9942,13 @@
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="55" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>272</v>
@@ -9887,19 +9960,19 @@
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="55" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C15" s="62" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D15" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E15" s="105" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="F15" s="120" t="s">
         <v>134</v>
@@ -9907,19 +9980,19 @@
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C16" s="62" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="D16" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E16" s="108" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F16" s="120" t="s">
         <v>134</v>
@@ -9927,13 +10000,13 @@
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B17" s="104" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C17" s="107" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="D17" s="104" t="s">
         <v>272</v>
@@ -10052,7 +10125,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="39" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B7" s="44" t="s">
         <v>134</v>
@@ -10069,7 +10142,7 @@
         <v>128</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>133</v>
@@ -10122,7 +10195,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B12" s="44" t="s">
         <v>134</v>
@@ -10150,7 +10223,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B14" s="44" t="s">
         <v>134</v>
@@ -10206,7 +10279,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B18" s="44" t="s">
         <v>134</v>
@@ -10234,7 +10307,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B20" s="44" t="s">
         <v>134</v>
@@ -10281,7 +10354,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -10374,10 +10447,10 @@
         <v>575</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C7" s="100" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D7" s="67" t="s">
         <v>272</v>
@@ -10391,10 +10464,10 @@
         <v>575</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C8" s="100" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D8" s="70" t="s">
         <v>273</v>
@@ -10413,11 +10486,11 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="90.5703125" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="48.42578125" customWidth="1"/>
@@ -10441,7 +10514,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10452,10 +10525,10 @@
         <v>566</v>
       </c>
       <c r="C2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E2" s="47"/>
       <c r="F2" s="66" t="s">
@@ -10470,13 +10543,13 @@
         <v>598</v>
       </c>
       <c r="C3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="F3" s="66" t="s">
         <v>134</v>
@@ -10490,13 +10563,13 @@
         <v>605</v>
       </c>
       <c r="C4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E4" s="62" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="F4" s="66" t="s">
         <v>134</v>
@@ -10504,19 +10577,19 @@
     </row>
     <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B5" s="47" t="s">
         <v>608</v>
       </c>
       <c r="C5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E5" s="62" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="F5" s="66" t="s">
         <v>134</v>
@@ -10524,50 +10597,50 @@
     </row>
     <row r="6" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>609</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E6" s="62" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="F6" s="120" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>611</v>
+        <v>918</v>
       </c>
       <c r="C7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>841</v>
+        <v>928</v>
       </c>
       <c r="F7" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C8" s="47" t="s">
         <v>337</v>
@@ -10576,7 +10649,7 @@
         <v>272</v>
       </c>
       <c r="E8" s="62" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F8" s="120" t="s">
         <v>134</v>
@@ -10584,13 +10657,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B9" s="47" t="s">
+        <v>663</v>
+      </c>
+      <c r="C9" t="s">
         <v>664</v>
-      </c>
-      <c r="C9" t="s">
-        <v>665</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>272</v>
@@ -10602,19 +10675,19 @@
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C10" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D10" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E10" s="62" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F10" s="120" t="s">
         <v>134</v>
@@ -10622,19 +10695,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="110" t="s">
+        <v>715</v>
+      </c>
+      <c r="B11" s="110" t="s">
         <v>716</v>
       </c>
-      <c r="B11" s="110" t="s">
+      <c r="C11" t="s">
         <v>717</v>
-      </c>
-      <c r="C11" t="s">
-        <v>718</v>
       </c>
       <c r="D11" s="110" t="s">
         <v>272</v>
       </c>
       <c r="E11" s="111" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="F11" s="120" t="s">
         <v>134</v>
@@ -10642,78 +10715,129 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B12" s="110" t="s">
+        <v>772</v>
+      </c>
+      <c r="C12" s="88" t="s">
         <v>774</v>
-      </c>
-      <c r="C12" s="88" t="s">
-        <v>776</v>
       </c>
       <c r="D12" s="110" t="s">
         <v>272</v>
       </c>
       <c r="F12" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="110" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B13" s="110" t="s">
+        <v>844</v>
+      </c>
+      <c r="C13" s="88" t="s">
         <v>847</v>
-      </c>
-      <c r="C13" s="88" t="s">
-        <v>850</v>
       </c>
       <c r="D13" s="110" t="s">
         <v>272</v>
       </c>
       <c r="E13" s="62" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F13" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="110" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B14" s="53" t="s">
+        <v>845</v>
+      </c>
+      <c r="C14" s="88" t="s">
         <v>848</v>
-      </c>
-      <c r="C14" s="88" t="s">
-        <v>851</v>
       </c>
       <c r="D14" s="53" t="s">
         <v>272</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="F14" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="110" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C15" s="109" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D15" s="109" t="s">
         <v>272</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="F15" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="110" t="s">
+        <v>919</v>
+      </c>
+      <c r="B16" s="141" t="s">
+        <v>921</v>
+      </c>
+      <c r="C16" s="88" t="s">
+        <v>547</v>
+      </c>
+      <c r="D16" s="141" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="110" t="s">
+        <v>920</v>
+      </c>
+      <c r="B17" s="141" t="s">
+        <v>922</v>
+      </c>
+      <c r="C17" t="s">
+        <v>926</v>
+      </c>
+      <c r="D17" s="141" t="s">
+        <v>272</v>
+      </c>
+      <c r="F17" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="110" t="s">
+        <v>924</v>
+      </c>
+      <c r="B18" s="141" t="s">
+        <v>923</v>
+      </c>
+      <c r="C18" s="88" t="s">
+        <v>927</v>
+      </c>
+      <c r="D18" s="141" t="s">
+        <v>272</v>
+      </c>
+      <c r="F18" s="120" t="s">
         <v>134</v>
       </c>
     </row>
@@ -13247,7 +13371,7 @@
         <v>93</v>
       </c>
       <c r="B2" s="96" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13255,7 +13379,7 @@
         <v>94</v>
       </c>
       <c r="B3" s="96" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13263,20 +13387,20 @@
         <v>602</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B6" s="44" t="s">
         <v>89</v>
@@ -13284,10 +13408,10 @@
     </row>
     <row r="7" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13295,23 +13419,23 @@
         <v>16</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13319,15 +13443,15 @@
         <v>16</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B12" s="101" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13335,36 +13459,36 @@
         <v>91</v>
       </c>
       <c r="B13" s="101" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
+        <v>647</v>
+      </c>
+      <c r="B14" s="44" t="s">
         <v>648</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B16" s="101" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B17" s="44" t="s">
         <v>584</v>
@@ -13372,7 +13496,7 @@
     </row>
     <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B18" s="44" t="s">
         <v>584</v>
@@ -13380,10 +13504,10 @@
     </row>
     <row r="19" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13396,74 +13520,74 @@
     </row>
     <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13527,12 +13651,12 @@
         <v>136</v>
       </c>
       <c r="F1" s="72" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B2" s="121" t="s">
         <v>137</v>
@@ -13552,7 +13676,7 @@
     </row>
     <row r="3" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B3" s="118" t="s">
         <v>312</v>
@@ -13572,7 +13696,7 @@
     </row>
     <row r="4" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B4" s="51" t="s">
         <v>142</v>
@@ -13592,7 +13716,7 @@
     </row>
     <row r="5" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B5" s="118" t="s">
         <v>138</v>
@@ -13612,7 +13736,7 @@
     </row>
     <row r="6" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B6" s="51" t="s">
         <v>309</v>
@@ -13632,7 +13756,7 @@
     </row>
     <row r="7" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B7" s="48" t="s">
         <v>140</v>
@@ -13650,7 +13774,7 @@
     </row>
     <row r="8" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B8" s="51" t="s">
         <v>141</v>
@@ -13668,7 +13792,7 @@
     </row>
     <row r="9" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="B9" s="48" t="s">
         <v>139</v>
@@ -13684,7 +13808,7 @@
     </row>
     <row r="10" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>314</v>
@@ -13704,7 +13828,7 @@
     </row>
     <row r="11" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B11" s="48" t="s">
         <v>313</v>
@@ -13861,7 +13985,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="122" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -14122,7 +14246,7 @@
         <v>136</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14133,7 +14257,7 @@
         <v>319</v>
       </c>
       <c r="C2" s="117" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D2" s="47">
         <v>1</v>
@@ -14153,7 +14277,7 @@
         <v>310</v>
       </c>
       <c r="C3" s="117" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D3" s="47">
         <v>1</v>
@@ -14173,7 +14297,7 @@
         <v>311</v>
       </c>
       <c r="C4" s="117" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D4" s="47">
         <v>0</v>
@@ -14193,7 +14317,7 @@
         <v>148</v>
       </c>
       <c r="C5" s="117" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D5" s="47">
         <v>1</v>
@@ -14580,7 +14704,7 @@
         <v>136</v>
       </c>
       <c r="X1" s="124" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -14588,16 +14712,16 @@
         <v>205</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D2" s="30">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="E2" s="30">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -14613,13 +14737,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O2" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P2" s="12" t="s">
         <v>39</v>
@@ -14631,7 +14755,7 @@
         <v>29</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T2" s="14">
         <v>1000</v>
@@ -14640,7 +14764,7 @@
         <v>31</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W2" s="12" t="s">
         <v>272</v>
@@ -14654,10 +14778,10 @@
         <v>206</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D3" s="30">
         <v>46211</v>
@@ -14669,7 +14793,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H3" s="30">
         <v>46242</v>
@@ -14683,13 +14807,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O3" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>39</v>
@@ -14701,7 +14825,7 @@
         <v>29</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T3" s="14">
         <v>1000</v>
@@ -14710,7 +14834,7 @@
         <v>31</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W3" s="12" t="s">
         <v>272</v>
@@ -14724,10 +14848,10 @@
         <v>207</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D4" s="30">
         <v>46211</v>
@@ -14739,13 +14863,13 @@
         <v>390</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H4" s="30">
         <v>46248</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13">
@@ -14755,13 +14879,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O4" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>39</v>
@@ -14773,7 +14897,7 @@
         <v>29</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T4" s="14">
         <v>1000</v>
@@ -14782,7 +14906,7 @@
         <v>31</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W4" s="12" t="s">
         <v>272</v>
@@ -14796,10 +14920,10 @@
         <v>208</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="D5" s="30">
         <v>46211</v>
@@ -14811,7 +14935,7 @@
         <v>391</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H5" s="30">
         <v>46264</v>
@@ -14827,13 +14951,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O5" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>39</v>
@@ -14845,7 +14969,7 @@
         <v>29</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T5" s="14">
         <v>1000</v>
@@ -14854,7 +14978,7 @@
         <v>31</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W5" s="12" t="s">
         <v>272</v>
@@ -14868,10 +14992,10 @@
         <v>209</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D6" s="30">
         <v>46211</v>
@@ -14883,7 +15007,7 @@
         <v>392</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H6" s="30">
         <v>46264</v>
@@ -14899,13 +15023,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O6" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P6" s="12" t="s">
         <v>39</v>
@@ -14917,7 +15041,7 @@
         <v>29</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T6" s="14">
         <v>1000</v>
@@ -14926,7 +15050,7 @@
         <v>31</v>
       </c>
       <c r="V6" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W6" s="12" t="s">
         <v>272</v>
@@ -14940,10 +15064,10 @@
         <v>210</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D7" s="30">
         <v>46211</v>
@@ -14955,7 +15079,7 @@
         <v>395</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H7" s="30">
         <v>46417</v>
@@ -14971,13 +15095,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O7" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P7" s="12" t="s">
         <v>39</v>
@@ -14989,7 +15113,7 @@
         <v>29</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T7" s="14">
         <v>1000</v>
@@ -14998,7 +15122,7 @@
         <v>31</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W7" s="12" t="s">
         <v>272</v>
@@ -15012,10 +15136,10 @@
         <v>211</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="D8" s="30">
         <v>46211</v>
@@ -15027,7 +15151,7 @@
         <v>393</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H8" s="30">
         <v>46537</v>
@@ -15043,13 +15167,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O8" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P8" s="12" t="s">
         <v>39</v>
@@ -15061,7 +15185,7 @@
         <v>29</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T8" s="14">
         <v>1000</v>
@@ -15070,7 +15194,7 @@
         <v>31</v>
       </c>
       <c r="V8" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W8" s="12" t="s">
         <v>272</v>
@@ -15084,10 +15208,10 @@
         <v>212</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D9" s="30">
         <v>46211</v>
@@ -15099,7 +15223,7 @@
         <v>397</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H9" s="30">
         <v>46264</v>
@@ -15115,13 +15239,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O9" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>39</v>
@@ -15133,7 +15257,7 @@
         <v>29</v>
       </c>
       <c r="S9" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="T9" s="14">
         <v>1000</v>
@@ -15142,7 +15266,7 @@
         <v>31</v>
       </c>
       <c r="V9" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W9" s="12" t="s">
         <v>272</v>
@@ -17255,7 +17379,7 @@
     </row>
     <row r="51" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="48" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B51" s="56" t="s">
         <v>394</v>
@@ -17297,7 +17421,7 @@
     </row>
     <row r="52" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="48" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B52" s="56" t="s">
         <v>331</v>
@@ -17339,7 +17463,7 @@
     </row>
     <row r="53" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="48" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B53" s="56" t="s">
         <v>396</v>
@@ -17381,7 +17505,7 @@
     </row>
     <row r="54" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="48" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B54" s="56" t="s">
         <v>332</v>
@@ -17423,7 +17547,7 @@
     </row>
     <row r="55" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="48" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B55" s="56" t="s">
         <v>333</v>
@@ -17467,7 +17591,7 @@
     </row>
     <row r="56" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="48" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B56" s="56" t="s">
         <v>334</v>
@@ -17509,7 +17633,7 @@
     </row>
     <row r="57" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="48" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B57" s="56" t="s">
         <v>335</v>
@@ -17551,7 +17675,7 @@
     </row>
     <row r="58" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="48" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B58" s="56" t="s">
         <v>336</v>
@@ -18350,7 +18474,7 @@
         <v>136</v>
       </c>
       <c r="Y1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -18361,13 +18485,13 @@
         <v>150</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D2" s="30">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="E2" s="30">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -18383,13 +18507,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O2" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P2" s="47" t="s">
         <v>39</v>
@@ -18398,7 +18522,7 @@
         <v>28</v>
       </c>
       <c r="R2" s="47" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S2" s="47" t="s">
         <v>29</v>
@@ -18413,7 +18537,7 @@
         <v>31</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>272</v>
@@ -18427,10 +18551,10 @@
         <v>238</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D3" s="30">
         <v>46211</v>
@@ -18442,7 +18566,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H3" s="30">
         <v>46242</v>
@@ -18456,13 +18580,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O3" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P3" s="47" t="s">
         <v>39</v>
@@ -18471,13 +18595,13 @@
         <v>28</v>
       </c>
       <c r="R3" s="47" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S3" s="47" t="s">
         <v>29</v>
       </c>
       <c r="T3" s="47" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U3" s="47">
         <v>1000</v>
@@ -18486,7 +18610,7 @@
         <v>31</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="X3" s="12" t="s">
         <v>272</v>
@@ -18500,10 +18624,10 @@
         <v>239</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D4" s="30">
         <v>46211</v>
@@ -18515,13 +18639,13 @@
         <v>390</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H4" s="30">
         <v>46248</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13">
@@ -18531,13 +18655,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O4" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P4" s="47" t="s">
         <v>39</v>
@@ -18546,13 +18670,13 @@
         <v>28</v>
       </c>
       <c r="R4" s="47" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S4" s="47" t="s">
         <v>29</v>
       </c>
       <c r="T4" s="47" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U4" s="47">
         <v>1000</v>
@@ -18561,7 +18685,7 @@
         <v>31</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="X4" s="12" t="s">
         <v>272</v>
@@ -18575,10 +18699,10 @@
         <v>240</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="D5" s="30">
         <v>46211</v>
@@ -18590,7 +18714,7 @@
         <v>391</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H5" s="30">
         <v>46264</v>
@@ -18606,13 +18730,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O5" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P5" s="47" t="s">
         <v>39</v>
@@ -18621,13 +18745,13 @@
         <v>28</v>
       </c>
       <c r="R5" s="47" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S5" s="47" t="s">
         <v>29</v>
       </c>
       <c r="T5" s="47" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U5" s="47">
         <v>1000</v>
@@ -18636,7 +18760,7 @@
         <v>31</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="X5" s="12" t="s">
         <v>272</v>
@@ -18650,10 +18774,10 @@
         <v>241</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D6" s="30">
         <v>46211</v>
@@ -18665,7 +18789,7 @@
         <v>392</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H6" s="30">
         <v>46264</v>
@@ -18681,13 +18805,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O6" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P6" s="47" t="s">
         <v>39</v>
@@ -18696,13 +18820,13 @@
         <v>28</v>
       </c>
       <c r="R6" s="47" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S6" s="47" t="s">
         <v>29</v>
       </c>
       <c r="T6" s="47" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U6" s="47">
         <v>1000</v>
@@ -18711,7 +18835,7 @@
         <v>31</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="X6" s="12" t="s">
         <v>272</v>
@@ -18725,10 +18849,10 @@
         <v>242</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D7" s="30">
         <v>46211</v>
@@ -18740,7 +18864,7 @@
         <v>395</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H7" s="30">
         <v>46417</v>
@@ -18756,13 +18880,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O7" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P7" s="47" t="s">
         <v>39</v>
@@ -18771,13 +18895,13 @@
         <v>28</v>
       </c>
       <c r="R7" s="47" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S7" s="47" t="s">
         <v>29</v>
       </c>
       <c r="T7" s="47" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U7" s="47">
         <v>1000</v>
@@ -18786,7 +18910,7 @@
         <v>31</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="X7" s="12" t="s">
         <v>272</v>
@@ -18800,10 +18924,10 @@
         <v>243</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="D8" s="30">
         <v>46211</v>
@@ -18815,7 +18939,7 @@
         <v>393</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H8" s="30">
         <v>46537</v>
@@ -18831,13 +18955,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O8" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P8" s="47" t="s">
         <v>39</v>
@@ -18846,13 +18970,13 @@
         <v>28</v>
       </c>
       <c r="R8" s="47" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S8" s="47" t="s">
         <v>29</v>
       </c>
       <c r="T8" s="47" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U8" s="47">
         <v>1000</v>
@@ -18861,7 +18985,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="X8" s="12" t="s">
         <v>272</v>
@@ -18875,10 +18999,10 @@
         <v>244</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D9" s="30">
         <v>46211</v>
@@ -18890,7 +19014,7 @@
         <v>397</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="H9" s="30">
         <v>46233</v>
@@ -18906,13 +19030,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="O9" s="44" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="P9" s="47" t="s">
         <v>39</v>
@@ -18921,13 +19045,13 @@
         <v>28</v>
       </c>
       <c r="R9" s="47" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="S9" s="47" t="s">
         <v>29</v>
       </c>
       <c r="T9" s="47" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U9" s="47">
         <v>1000</v>
@@ -18936,7 +19060,7 @@
         <v>31</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="X9" s="12" t="s">
         <v>272</v>
@@ -21197,7 +21321,7 @@
     </row>
     <row r="52" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="47" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B52" s="47" t="s">
         <v>330</v>
@@ -21242,7 +21366,7 @@
     </row>
     <row r="53" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="47" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B53" s="78" t="s">
         <v>331</v>
@@ -21287,7 +21411,7 @@
     </row>
     <row r="54" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="47" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B54" s="47" t="s">
         <v>332</v>
@@ -21334,7 +21458,7 @@
     </row>
     <row r="55" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="47" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B55" s="78" t="s">
         <v>333</v>
@@ -21379,7 +21503,7 @@
     </row>
     <row r="56" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="47" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B56" s="47" t="s">
         <v>334</v>
@@ -21424,7 +21548,7 @@
     </row>
     <row r="57" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="47" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B57" s="78" t="s">
         <v>335</v>
@@ -21469,7 +21593,7 @@
     </row>
     <row r="58" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="47" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B58" s="47" t="s">
         <v>336</v>
@@ -22536,18 +22660,18 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C2" s="62" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
@@ -22558,13 +22682,13 @@
     </row>
     <row r="3" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B3" s="47" t="s">
+        <v>818</v>
+      </c>
+      <c r="C3" s="62" t="s">
         <v>820</v>
-      </c>
-      <c r="C3" s="62" t="s">
-        <v>822</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>272</v>
@@ -22575,13 +22699,13 @@
     </row>
     <row r="4" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C4" s="62" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>272</v>
@@ -22592,13 +22716,13 @@
     </row>
     <row r="5" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -22609,13 +22733,13 @@
     </row>
     <row r="6" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>272</v>
@@ -22626,13 +22750,13 @@
     </row>
     <row r="7" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C7" s="62" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>272</v>
@@ -22643,13 +22767,13 @@
     </row>
     <row r="8" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>272</v>
@@ -22660,13 +22784,13 @@
     </row>
     <row r="9" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>272</v>
@@ -22677,13 +22801,13 @@
     </row>
     <row r="10" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C10" s="62" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D10" s="47" t="s">
         <v>272</v>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -2851,13 +2851,13 @@
     <t>Test the Task_Only_once 15_07</t>
   </si>
   <si>
-    <t>{"company_name" : "Test the Company_2199", "license_name":"BSE"}</t>
-  </si>
-  <si>
     <t>{"company_name":"Test Company_1213", "license_name":"BSE"}</t>
   </si>
   <si>
     <t>Test Update Task</t>
+  </si>
+  <si>
+    <t>{"company_name" : "Test Company_4056", "license_name":"BSE"}</t>
   </si>
 </sst>
 </file>
@@ -9739,7 +9739,7 @@
         <v>813</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -9831,7 +9831,7 @@
         <v>814</v>
       </c>
       <c r="F7" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -10294,7 +10294,7 @@
         <v>611</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>133</v>
@@ -10308,7 +10308,7 @@
         <v>599</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C19" s="95" t="s">
         <v>133</v>
@@ -10641,10 +10641,10 @@
         <v>272</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F7" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -10661,10 +10661,10 @@
         <v>272</v>
       </c>
       <c r="E8" s="62" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F8" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -29988,7 +29988,7 @@
         <v>645</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="31" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -31120,10 +31120,10 @@
         <v>930</v>
       </c>
       <c r="D2" s="30">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="E2" s="30">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -34890,10 +34890,10 @@
         <v>860</v>
       </c>
       <c r="D2" s="30">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="E2" s="30">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="1"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="7" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="933">
   <si>
     <t>task_name</t>
   </si>
@@ -2638,9 +2638,6 @@
     <t>rahuld@secmark.in</t>
   </si>
   <si>
-    <t>Test the Task_Only_once 29-06</t>
-  </si>
-  <si>
     <t>bulk_task_creation</t>
   </si>
   <si>
@@ -2848,9 +2845,6 @@
     <t>{"normal_task":"Test Normal Task"}</t>
   </si>
   <si>
-    <t>Test the Task_Only_once 15_07</t>
-  </si>
-  <si>
     <t>{"company_name":"Test Company_1213", "license_name":"BSE"}</t>
   </si>
   <si>
@@ -2858,6 +2852,9 @@
   </si>
   <si>
     <t>{"company_name" : "Test Company_4056", "license_name":"BSE"}</t>
+  </si>
+  <si>
+    <t>Test the Task_Only_once 21-07</t>
   </si>
 </sst>
 </file>
@@ -6552,7 +6549,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -6696,7 +6693,7 @@
       </c>
       <c r="E9" s="62"/>
       <c r="F9" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -7136,16 +7133,16 @@
         <v>820</v>
       </c>
       <c r="B34" s="110" t="s">
+        <v>860</v>
+      </c>
+      <c r="C34" t="s">
         <v>861</v>
-      </c>
-      <c r="C34" t="s">
-        <v>862</v>
       </c>
       <c r="D34" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F34" s="66" t="s">
         <v>134</v>
@@ -7177,7 +7174,7 @@
         <v>821</v>
       </c>
       <c r="C36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D36" s="82" t="s">
         <v>272</v>
@@ -7191,7 +7188,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B37" s="115" t="s">
         <v>850</v>
@@ -7209,7 +7206,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="47" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B38" s="115" t="s">
         <v>851</v>
@@ -7227,19 +7224,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="47" t="s">
+        <v>902</v>
+      </c>
+      <c r="B39" s="115" t="s">
         <v>903</v>
       </c>
-      <c r="B39" s="115" t="s">
+      <c r="C39" s="140" t="s">
         <v>904</v>
-      </c>
-      <c r="C39" s="140" t="s">
-        <v>905</v>
       </c>
       <c r="D39" s="116" t="s">
         <v>272</v>
       </c>
       <c r="E39" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F39" s="66" t="s">
         <v>134</v>
@@ -7247,22 +7244,22 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="47" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B40" s="47" t="s">
         <v>619</v>
       </c>
       <c r="C40" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D40" s="67" t="s">
         <v>272</v>
       </c>
       <c r="E40" s="66" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F40" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -7323,7 +7320,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7730,7 +7727,7 @@
         <v>528</v>
       </c>
       <c r="C24" s="139" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D24" s="82" t="s">
         <v>272</v>
@@ -7781,16 +7778,16 @@
         <v>521</v>
       </c>
       <c r="B27" s="110" t="s">
+        <v>860</v>
+      </c>
+      <c r="C27" t="s">
         <v>861</v>
-      </c>
-      <c r="C27" t="s">
-        <v>862</v>
       </c>
       <c r="D27" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E27" s="62" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F27" s="66" t="s">
         <v>134</v>
@@ -7888,7 +7885,7 @@
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="86" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B33" s="82" t="s">
         <v>460</v>
@@ -7906,19 +7903,19 @@
     </row>
     <row r="34" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="86" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>831</v>
       </c>
       <c r="C34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D34" s="116" t="s">
         <v>272</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F34" s="66" t="s">
         <v>134</v>
@@ -7926,19 +7923,19 @@
     </row>
     <row r="35" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="86" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B35" s="47" t="s">
         <v>632</v>
       </c>
       <c r="C35" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D35" s="70" t="s">
         <v>272</v>
       </c>
       <c r="E35" s="66" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F35" s="66" t="s">
         <v>133</v>
@@ -8024,7 +8021,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -8462,7 +8459,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -8729,7 +8726,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -8740,7 +8737,7 @@
         <v>855</v>
       </c>
       <c r="C2" s="87" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D2" s="67" t="s">
         <v>272</v>
@@ -8757,7 +8754,7 @@
         <v>856</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D3" t="s">
         <v>272</v>
@@ -8922,7 +8919,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -9269,7 +9266,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -9440,7 +9437,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -9485,7 +9482,7 @@
         <v>711</v>
       </c>
       <c r="C4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>272</v>
@@ -9502,7 +9499,7 @@
         <v>719</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -9550,7 +9547,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -9671,7 +9668,7 @@
         <v>832</v>
       </c>
       <c r="C8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D8" s="118" t="s">
         <v>272</v>
@@ -9719,7 +9716,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -9730,7 +9727,7 @@
         <v>564</v>
       </c>
       <c r="C2" s="62" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
@@ -9750,7 +9747,7 @@
         <v>593</v>
       </c>
       <c r="C3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>272</v>
@@ -9822,7 +9819,7 @@
         <v>666</v>
       </c>
       <c r="C7" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>272</v>
@@ -9842,7 +9839,7 @@
         <v>665</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>272</v>
@@ -9942,7 +9939,7 @@
         <v>757</v>
       </c>
       <c r="C13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>272</v>
@@ -9960,7 +9957,7 @@
         <v>686</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>272</v>
@@ -9978,7 +9975,7 @@
         <v>627</v>
       </c>
       <c r="C15" s="62" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D15" s="47" t="s">
         <v>272</v>
@@ -9998,7 +9995,7 @@
         <v>628</v>
       </c>
       <c r="C16" s="62" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D16" s="47" t="s">
         <v>272</v>
@@ -10018,7 +10015,7 @@
         <v>626</v>
       </c>
       <c r="C17" s="107" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D17" s="104" t="s">
         <v>272</v>
@@ -10154,7 +10151,7 @@
         <v>128</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>133</v>
@@ -10308,7 +10305,7 @@
         <v>599</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="95" t="s">
         <v>133</v>
@@ -10366,7 +10363,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -10526,7 +10523,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10632,7 +10629,7 @@
         <v>629</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C7" t="s">
         <v>701</v>
@@ -10641,7 +10638,7 @@
         <v>272</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F7" s="120" t="s">
         <v>133</v>
@@ -10661,7 +10658,7 @@
         <v>272</v>
       </c>
       <c r="E8" s="62" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="F8" s="120" t="s">
         <v>134</v>
@@ -10776,7 +10773,7 @@
         <v>272</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F14" s="120" t="s">
         <v>134</v>
@@ -10804,10 +10801,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="110" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B16" s="141" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C16" s="88" t="s">
         <v>547</v>
@@ -10821,13 +10818,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="110" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B17" s="141" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C17" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D17" s="141" t="s">
         <v>272</v>
@@ -10838,13 +10835,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="110" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B18" s="141" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C18" s="88" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D18" s="141" t="s">
         <v>272</v>
@@ -13399,7 +13396,7 @@
         <v>602</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13500,10 +13497,10 @@
     </row>
     <row r="17" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C17" s="66"/>
       <c r="D17" s="66"/>
@@ -29924,7 +29921,7 @@
         <v>633</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="23" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -29948,7 +29945,7 @@
         <v>635</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="26" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -29964,7 +29961,7 @@
         <v>656</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="28" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -29972,7 +29969,7 @@
         <v>644</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="29" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -29980,7 +29977,7 @@
         <v>643</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="30" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -29988,7 +29985,7 @@
         <v>645</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="31" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -30053,12 +30050,12 @@
         <v>136</v>
       </c>
       <c r="F1" s="72" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B2" s="121" t="s">
         <v>137</v>
@@ -30078,7 +30075,7 @@
     </row>
     <row r="3" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B3" s="118" t="s">
         <v>312</v>
@@ -30098,7 +30095,7 @@
     </row>
     <row r="4" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B4" s="51" t="s">
         <v>142</v>
@@ -30118,7 +30115,7 @@
     </row>
     <row r="5" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B5" s="118" t="s">
         <v>138</v>
@@ -30138,7 +30135,7 @@
     </row>
     <row r="6" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B6" s="51" t="s">
         <v>309</v>
@@ -30158,7 +30155,7 @@
     </row>
     <row r="7" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B7" s="48" t="s">
         <v>140</v>
@@ -30176,7 +30173,7 @@
     </row>
     <row r="8" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B8" s="51" t="s">
         <v>141</v>
@@ -30194,7 +30191,7 @@
     </row>
     <row r="9" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B9" s="48" t="s">
         <v>139</v>
@@ -30210,7 +30207,7 @@
     </row>
     <row r="10" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>314</v>
@@ -30230,7 +30227,7 @@
     </row>
     <row r="11" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B11" s="48" t="s">
         <v>313</v>
@@ -30387,7 +30384,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="122" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -30648,7 +30645,7 @@
         <v>136</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31106,7 +31103,7 @@
         <v>136</v>
       </c>
       <c r="X1" s="124" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -31117,13 +31114,13 @@
         <v>729</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="D2" s="30">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="E2" s="30">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -31183,7 +31180,7 @@
         <v>730</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D3" s="30">
         <v>46218</v>
@@ -31253,7 +31250,7 @@
         <v>731</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D4" s="30">
         <v>46218</v>
@@ -31325,7 +31322,7 @@
         <v>732</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D5" s="30">
         <v>46218</v>
@@ -31397,7 +31394,7 @@
         <v>733</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D6" s="30">
         <v>46218</v>
@@ -31469,7 +31466,7 @@
         <v>734</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D7" s="30">
         <v>46218</v>
@@ -31541,7 +31538,7 @@
         <v>735</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D8" s="30">
         <v>46218</v>
@@ -31613,7 +31610,7 @@
         <v>736</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D9" s="30">
         <v>46218</v>
@@ -34876,7 +34873,7 @@
         <v>136</v>
       </c>
       <c r="Y1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -34887,13 +34884,13 @@
         <v>150</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>860</v>
+        <v>932</v>
       </c>
       <c r="D2" s="30">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="E2" s="30">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -34956,7 +34953,7 @@
         <v>730</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D3" s="30">
         <v>46211</v>
@@ -35029,7 +35026,7 @@
         <v>731</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D4" s="30">
         <v>46211</v>
@@ -35104,7 +35101,7 @@
         <v>732</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D5" s="30">
         <v>46211</v>
@@ -35179,7 +35176,7 @@
         <v>733</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D6" s="30">
         <v>46211</v>
@@ -35254,7 +35251,7 @@
         <v>734</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D7" s="30">
         <v>46211</v>
@@ -35329,7 +35326,7 @@
         <v>735</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D8" s="30">
         <v>46211</v>
@@ -35404,7 +35401,7 @@
         <v>736</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D9" s="30">
         <v>46211</v>
@@ -39062,7 +39059,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="7" activeTab="9"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="939">
   <si>
     <t>task_name</t>
   </si>
@@ -2855,6 +2855,24 @@
   </si>
   <si>
     <t>Test the Task_Only_once 21-07</t>
+  </si>
+  <si>
+    <t>Verify column filter search functionality using the first available values.</t>
+  </si>
+  <si>
+    <t>TC_SP_DASHBOARD_35</t>
+  </si>
+  <si>
+    <t>special_comment_task</t>
+  </si>
+  <si>
+    <t>Verify that a comment can be added to a Special Task when comments are enabled.</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>preprod</t>
   </si>
 </sst>
 </file>
@@ -3019,6 +3037,7 @@
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -5897,13 +5916,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:D3" totalsRowShown="0">
-  <autoFilter ref="A1:D3"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:E3" totalsRowShown="0">
+  <autoFilter ref="A1:E3"/>
+  <tableColumns count="5">
     <tableColumn id="1" name="username" dataCellStyle="Hyperlink"/>
     <tableColumn id="2" name="password" dataCellStyle="Hyperlink"/>
     <tableColumn id="3" name="browser" dataCellStyle="Hyperlink"/>
     <tableColumn id="4" name="usertype" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" name="website" dataCellStyle="Hyperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6463,16 +6483,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" style="36" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" style="36" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
         <v>93</v>
       </c>
@@ -6485,8 +6506,11 @@
       <c r="D1" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>859</v>
       </c>
@@ -6499,12 +6523,16 @@
       <c r="D2" s="93" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="42"/>
       <c r="B3" s="42"/>
       <c r="C3" s="89"/>
       <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6603,7 +6631,7 @@
       </c>
       <c r="E4" s="62"/>
       <c r="F4" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -6693,7 +6721,7 @@
       </c>
       <c r="E9" s="62"/>
       <c r="F9" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -7938,11 +7966,26 @@
         <v>918</v>
       </c>
       <c r="F35" s="66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="86" t="s">
+        <v>934</v>
+      </c>
+      <c r="B36" s="47" t="s">
+        <v>935</v>
+      </c>
+      <c r="C36" t="s">
+        <v>936</v>
+      </c>
+      <c r="D36" s="70" t="s">
+        <v>272</v>
+      </c>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F36" s="66"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F37" s="66"/>
@@ -8123,7 +8166,7 @@
         <v>272</v>
       </c>
       <c r="E7" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -8140,7 +8183,7 @@
         <v>272</v>
       </c>
       <c r="E8" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -8476,7 +8519,7 @@
         <v>272</v>
       </c>
       <c r="E2" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -8493,7 +8536,7 @@
         <v>272</v>
       </c>
       <c r="E3" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8510,7 +8553,7 @@
         <v>272</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -9447,8 +9490,8 @@
       <c r="B2" s="47" t="s">
         <v>695</v>
       </c>
-      <c r="C2" t="s">
-        <v>337</v>
+      <c r="C2" s="88" t="s">
+        <v>933</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
@@ -9585,7 +9628,7 @@
       </c>
       <c r="E3" s="62"/>
       <c r="F3" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -9623,7 +9666,7 @@
         <v>759</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -9657,7 +9700,7 @@
         <v>272</v>
       </c>
       <c r="F7" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -9736,7 +9779,7 @@
         <v>813</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -9828,7 +9871,7 @@
         <v>814</v>
       </c>
       <c r="F7" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -9848,7 +9891,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -9984,7 +10027,7 @@
         <v>816</v>
       </c>
       <c r="F15" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -10004,7 +10047,7 @@
         <v>814</v>
       </c>
       <c r="F16" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -10022,7 +10065,7 @@
       </c>
       <c r="E17" s="70"/>
       <c r="F17" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -10151,7 +10194,7 @@
         <v>128</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>133</v>
@@ -10165,7 +10208,7 @@
         <v>535</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="44" t="s">
         <v>133</v>
@@ -10641,7 +10684,7 @@
         <v>931</v>
       </c>
       <c r="F7" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -10796,7 +10839,7 @@
         <v>846</v>
       </c>
       <c r="F15" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -31117,10 +31160,10 @@
         <v>932</v>
       </c>
       <c r="D2" s="30">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="E2" s="30">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>
@@ -31183,10 +31226,10 @@
         <v>877</v>
       </c>
       <c r="D3" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="E3" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>25</v>
@@ -31239,7 +31282,7 @@
         <v>272</v>
       </c>
       <c r="X3" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -31253,10 +31296,10 @@
         <v>878</v>
       </c>
       <c r="D4" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="E4" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>390</v>
@@ -31311,7 +31354,7 @@
         <v>272</v>
       </c>
       <c r="X4" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -31325,10 +31368,10 @@
         <v>879</v>
       </c>
       <c r="D5" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="E5" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>391</v>
@@ -31383,7 +31426,7 @@
         <v>272</v>
       </c>
       <c r="X5" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -31397,10 +31440,10 @@
         <v>880</v>
       </c>
       <c r="D6" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="E6" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>392</v>
@@ -31455,7 +31498,7 @@
         <v>272</v>
       </c>
       <c r="X6" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -31469,10 +31512,10 @@
         <v>881</v>
       </c>
       <c r="D7" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="E7" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>395</v>
@@ -31527,7 +31570,7 @@
         <v>272</v>
       </c>
       <c r="X7" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -31541,10 +31584,10 @@
         <v>882</v>
       </c>
       <c r="D8" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="E8" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>393</v>
@@ -31599,7 +31642,7 @@
         <v>272</v>
       </c>
       <c r="X8" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -31613,10 +31656,10 @@
         <v>883</v>
       </c>
       <c r="D9" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="E9" s="30">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>397</v>
@@ -31671,7 +31714,7 @@
         <v>272</v>
       </c>
       <c r="X9" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -34887,10 +34930,10 @@
         <v>932</v>
       </c>
       <c r="D2" s="30">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="E2" s="30">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>104</v>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" firstSheet="19" activeTab="21"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,8 @@
     <sheet name="project_test_cases" sheetId="19" r:id="rId19"/>
     <sheet name="normal_task_sections_test_cases" sheetId="15" r:id="rId20"/>
     <sheet name="settings_test_cases" sheetId="17" r:id="rId21"/>
-    <sheet name="helper" sheetId="8" r:id="rId22"/>
+    <sheet name="audit_test_cases" sheetId="26" r:id="rId22"/>
+    <sheet name="helper" sheetId="8" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">dashboard_test_cases!$A$1:$D$26</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="959">
   <si>
     <t>task_name</t>
   </si>
@@ -2209,9 +2210,6 @@
     <t>Verify that column filters in Compliance Events work correctly using the first available values.</t>
   </si>
   <si>
-    <t>Verify that the Issuer link and Dashboard are clickable and navigate to the correct pages</t>
-  </si>
-  <si>
     <t>Verify that a task can be created under "Create Your Own Task" in Updates and is displayed on the Dashboard.</t>
   </si>
   <si>
@@ -2873,6 +2871,69 @@
   </si>
   <si>
     <t>preprod</t>
+  </si>
+  <si>
+    <t>TC_Settings_18</t>
+  </si>
+  <si>
+    <t>bulk_invitations</t>
+  </si>
+  <si>
+    <t>Verify bulk Invitations using Excel file upload</t>
+  </si>
+  <si>
+    <t>TC_Settings_19</t>
+  </si>
+  <si>
+    <t>bulk_invitation_download_template</t>
+  </si>
+  <si>
+    <t>Verify that the Issuer link and Download are clickable and navigate to the correct pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify bulk Invitation download is clickable </t>
+  </si>
+  <si>
+    <t>audit</t>
+  </si>
+  <si>
+    <t>audit_company</t>
+  </si>
+  <si>
+    <t>verify audit company details</t>
+  </si>
+  <si>
+    <t>TC_Audit_1</t>
+  </si>
+  <si>
+    <t>bhavani+69@secmark.in</t>
+  </si>
+  <si>
+    <t>{"email_id" : "testuser234@gmail.com"}</t>
+  </si>
+  <si>
+    <t>TC_Audit_2</t>
+  </si>
+  <si>
+    <t>audit_branch</t>
+  </si>
+  <si>
+    <t>verify audit branch details</t>
+  </si>
+  <si>
+    <t>TC_Audit_3</t>
+  </si>
+  <si>
+    <t>verify Export data details</t>
+  </si>
+  <si>
+    <t>TC_Audit_4</t>
+  </si>
+  <si>
+    <t>search_company_name</t>
+  </si>
+  <si>
+    <t>verify search company name  data details</t>
   </si>
 </sst>
 </file>
@@ -2885,7 +2946,7 @@
     <numFmt numFmtId="166" formatCode="dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="d\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3038,6 +3099,18 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3429,7 +3502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3781,6 +3854,12 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6054,8 +6133,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:D20" totalsRowShown="0" headerRowDxfId="119" dataDxfId="118">
-  <autoFilter ref="A1:D20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:D21" totalsRowShown="0" headerRowDxfId="119" dataDxfId="118">
+  <autoFilter ref="A1:D21"/>
   <tableColumns count="4">
     <tableColumn id="3" name="module_to_test" dataDxfId="117"/>
     <tableColumn id="4" name="execution" dataDxfId="116"/>
@@ -6507,24 +6586,24 @@
         <v>586</v>
       </c>
       <c r="E1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>859</v>
+        <v>949</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>670</v>
+        <v>339</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D2" s="93" t="s">
         <v>587</v>
       </c>
       <c r="E2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6577,7 +6656,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
@@ -7158,19 +7237,19 @@
     </row>
     <row r="34" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="47" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B34" s="110" t="s">
+        <v>859</v>
+      </c>
+      <c r="C34" t="s">
         <v>860</v>
-      </c>
-      <c r="C34" t="s">
-        <v>861</v>
       </c>
       <c r="D34" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F34" s="66" t="s">
         <v>134</v>
@@ -7178,7 +7257,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="47" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B35" s="110" t="s">
         <v>713</v>
@@ -7196,19 +7275,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="47" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B36" s="115" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C36" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D36" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E36" s="62" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F36" s="66" t="s">
         <v>134</v>
@@ -7216,10 +7295,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C37" s="88" t="s">
         <v>540</v>
@@ -7234,10 +7313,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="47" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B38" s="115" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C38" s="88" t="s">
         <v>491</v>
@@ -7252,19 +7331,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="47" t="s">
+        <v>901</v>
+      </c>
+      <c r="B39" s="115" t="s">
         <v>902</v>
       </c>
-      <c r="B39" s="115" t="s">
+      <c r="C39" s="140" t="s">
         <v>903</v>
-      </c>
-      <c r="C39" s="140" t="s">
-        <v>904</v>
       </c>
       <c r="D39" s="116" t="s">
         <v>272</v>
       </c>
       <c r="E39" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F39" s="66" t="s">
         <v>134</v>
@@ -7272,19 +7351,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="47" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B40" s="47" t="s">
         <v>619</v>
       </c>
       <c r="C40" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D40" s="67" t="s">
         <v>272</v>
       </c>
       <c r="E40" s="66" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F40" s="120" t="s">
         <v>134</v>
@@ -7348,7 +7427,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7374,7 +7453,7 @@
         <v>497</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C3" s="83" t="s">
         <v>469</v>
@@ -7410,7 +7489,7 @@
         <v>499</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C5" s="83" t="s">
         <v>475</v>
@@ -7755,7 +7834,7 @@
         <v>528</v>
       </c>
       <c r="C24" s="139" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D24" s="82" t="s">
         <v>272</v>
@@ -7806,16 +7885,16 @@
         <v>521</v>
       </c>
       <c r="B27" s="110" t="s">
+        <v>859</v>
+      </c>
+      <c r="C27" t="s">
         <v>860</v>
-      </c>
-      <c r="C27" t="s">
-        <v>861</v>
       </c>
       <c r="D27" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E27" s="62" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F27" s="66" t="s">
         <v>134</v>
@@ -7913,7 +7992,7 @@
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="86" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B33" s="82" t="s">
         <v>460</v>
@@ -7931,19 +8010,19 @@
     </row>
     <row r="34" spans="1:6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="86" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B34" s="115" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C34" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D34" s="116" t="s">
         <v>272</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F34" s="66" t="s">
         <v>134</v>
@@ -7951,19 +8030,19 @@
     </row>
     <row r="35" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="86" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B35" s="47" t="s">
         <v>632</v>
       </c>
       <c r="C35" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D35" s="70" t="s">
         <v>272</v>
       </c>
       <c r="E35" s="66" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F35" s="66" t="s">
         <v>134</v>
@@ -7971,13 +8050,13 @@
     </row>
     <row r="36" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="86" t="s">
+        <v>933</v>
+      </c>
+      <c r="B36" s="47" t="s">
         <v>934</v>
       </c>
-      <c r="B36" s="47" t="s">
+      <c r="C36" t="s">
         <v>935</v>
-      </c>
-      <c r="C36" t="s">
-        <v>936</v>
       </c>
       <c r="D36" s="70" t="s">
         <v>272</v>
@@ -8064,7 +8143,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -8502,7 +8581,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -8527,7 +8606,7 @@
         <v>297</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C3" t="s">
         <v>424</v>
@@ -8561,7 +8640,7 @@
         <v>302</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C5" s="48" t="s">
         <v>285</v>
@@ -8578,7 +8657,7 @@
         <v>304</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C6" s="46" t="s">
         <v>307</v>
@@ -8595,7 +8674,7 @@
         <v>305</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C7" s="62" t="s">
         <v>284</v>
@@ -8612,7 +8691,7 @@
         <v>306</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C8" s="62" t="s">
         <v>594</v>
@@ -8769,18 +8848,18 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
+        <v>853</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>854</v>
       </c>
-      <c r="B2" s="47" t="s">
-        <v>855</v>
-      </c>
       <c r="C2" s="87" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D2" s="67" t="s">
         <v>272</v>
@@ -8791,19 +8870,19 @@
     </row>
     <row r="3" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D3" t="s">
         <v>272</v>
       </c>
       <c r="E3" s="105" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F3" s="66" t="s">
         <v>133</v>
@@ -8962,7 +9041,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -9309,7 +9388,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -9317,10 +9396,10 @@
         <v>552</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>764</v>
+      </c>
+      <c r="C2" s="47" t="s">
         <v>765</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>766</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
@@ -9334,10 +9413,10 @@
         <v>553</v>
       </c>
       <c r="B3" s="113" t="s">
+        <v>766</v>
+      </c>
+      <c r="C3" s="113" t="s">
         <v>767</v>
-      </c>
-      <c r="C3" s="113" t="s">
-        <v>768</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>272</v>
@@ -9351,10 +9430,10 @@
         <v>554</v>
       </c>
       <c r="B4" s="47" t="s">
+        <v>768</v>
+      </c>
+      <c r="C4" s="113" t="s">
         <v>769</v>
-      </c>
-      <c r="C4" s="113" t="s">
-        <v>770</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>272</v>
@@ -9368,10 +9447,10 @@
         <v>555</v>
       </c>
       <c r="B5" s="47" t="s">
+        <v>770</v>
+      </c>
+      <c r="C5" s="113" t="s">
         <v>771</v>
-      </c>
-      <c r="C5" s="113" t="s">
-        <v>772</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -9385,10 +9464,10 @@
         <v>556</v>
       </c>
       <c r="B6" s="47" t="s">
+        <v>772</v>
+      </c>
+      <c r="C6" s="113" t="s">
         <v>773</v>
-      </c>
-      <c r="C6" s="113" t="s">
-        <v>774</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>272</v>
@@ -9402,10 +9481,10 @@
         <v>557</v>
       </c>
       <c r="B7" s="47" t="s">
+        <v>774</v>
+      </c>
+      <c r="C7" s="113" t="s">
         <v>775</v>
-      </c>
-      <c r="C7" s="113" t="s">
-        <v>776</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>272</v>
@@ -9419,10 +9498,10 @@
         <v>558</v>
       </c>
       <c r="B8" s="47" t="s">
+        <v>776</v>
+      </c>
+      <c r="C8" s="113" t="s">
         <v>777</v>
-      </c>
-      <c r="C8" s="113" t="s">
-        <v>778</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>272</v>
@@ -9480,7 +9559,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -9491,7 +9570,7 @@
         <v>695</v>
       </c>
       <c r="C2" s="88" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
@@ -9525,7 +9604,7 @@
         <v>711</v>
       </c>
       <c r="C4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>272</v>
@@ -9536,13 +9615,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -9590,7 +9669,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -9607,7 +9686,7 @@
         <v>272</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F2" s="66" t="s">
         <v>134</v>
@@ -9639,7 +9718,7 @@
         <v>682</v>
       </c>
       <c r="C4" t="s">
-        <v>717</v>
+        <v>943</v>
       </c>
       <c r="D4" s="118" t="s">
         <v>272</v>
@@ -9657,13 +9736,13 @@
         <v>577</v>
       </c>
       <c r="C5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D5" s="118" t="s">
         <v>272</v>
       </c>
       <c r="E5" s="62" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F5" s="66" t="s">
         <v>134</v>
@@ -9708,10 +9787,10 @@
         <v>683</v>
       </c>
       <c r="B8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C8" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D8" s="118" t="s">
         <v>272</v>
@@ -9759,7 +9838,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -9770,13 +9849,13 @@
         <v>564</v>
       </c>
       <c r="C2" s="62" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E2" s="105" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F2" s="66" t="s">
         <v>134</v>
@@ -9790,7 +9869,7 @@
         <v>593</v>
       </c>
       <c r="C3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>272</v>
@@ -9805,7 +9884,7 @@
         <v>615</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C4" s="88" t="s">
         <v>540</v>
@@ -9823,10 +9902,10 @@
         <v>624</v>
       </c>
       <c r="B5" s="47" t="s">
+        <v>721</v>
+      </c>
+      <c r="C5" s="88" t="s">
         <v>722</v>
-      </c>
-      <c r="C5" s="88" t="s">
-        <v>723</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -9841,7 +9920,7 @@
         <v>625</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>547</v>
@@ -9862,13 +9941,13 @@
         <v>666</v>
       </c>
       <c r="C7" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E7" s="108" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F7" s="66" t="s">
         <v>134</v>
@@ -9882,13 +9961,13 @@
         <v>665</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E8" s="105" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F8" s="120" t="s">
         <v>134</v>
@@ -9908,7 +9987,7 @@
         <v>272</v>
       </c>
       <c r="E9" s="108" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F9" s="120" t="s">
         <v>134</v>
@@ -9928,7 +10007,7 @@
         <v>272</v>
       </c>
       <c r="E10" s="105" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F10" s="120" t="s">
         <v>134</v>
@@ -9939,7 +10018,7 @@
         <v>691</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C11" s="62" t="s">
         <v>617</v>
@@ -9948,7 +10027,7 @@
         <v>272</v>
       </c>
       <c r="E11" s="108" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F11" s="120" t="s">
         <v>134</v>
@@ -9968,7 +10047,7 @@
         <v>272</v>
       </c>
       <c r="E12" s="105" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F12" s="120" t="s">
         <v>134</v>
@@ -9976,13 +10055,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="55" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C13" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>272</v>
@@ -9994,13 +10073,13 @@
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="55" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B14" s="47" t="s">
         <v>686</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>272</v>
@@ -10012,19 +10091,19 @@
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="55" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>627</v>
       </c>
       <c r="C15" s="62" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D15" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E15" s="105" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F15" s="120" t="s">
         <v>133</v>
@@ -10032,19 +10111,19 @@
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B16" s="47" t="s">
         <v>628</v>
       </c>
       <c r="C16" s="62" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D16" s="47" t="s">
         <v>272</v>
       </c>
       <c r="E16" s="108" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F16" s="120" t="s">
         <v>133</v>
@@ -10052,13 +10131,13 @@
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B17" s="104" t="s">
         <v>626</v>
       </c>
       <c r="C17" s="107" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D17" s="104" t="s">
         <v>272</v>
@@ -10081,7 +10160,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="17.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" style="39" bestFit="1" customWidth="1"/>
@@ -10177,7 +10256,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="39" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B7" s="44" t="s">
         <v>134</v>
@@ -10208,7 +10287,7 @@
         <v>535</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C9" s="44" t="s">
         <v>133</v>
@@ -10247,7 +10326,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B12" s="44" t="s">
         <v>134</v>
@@ -10359,7 +10438,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B20" s="44" t="s">
         <v>134</v>
@@ -10368,6 +10447,20 @@
         <v>133</v>
       </c>
       <c r="D20" s="114" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="143" t="s">
+        <v>945</v>
+      </c>
+      <c r="B21" s="144" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="144" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="144" t="s">
         <v>134</v>
       </c>
     </row>
@@ -10406,7 +10499,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -10538,7 +10631,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -10566,7 +10659,7 @@
         <v>606</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10601,7 +10694,7 @@
         <v>272</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F3" s="66" t="s">
         <v>134</v>
@@ -10621,7 +10714,7 @@
         <v>272</v>
       </c>
       <c r="E4" s="62" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="F4" s="66" t="s">
         <v>134</v>
@@ -10641,7 +10734,7 @@
         <v>272</v>
       </c>
       <c r="E5" s="62" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F5" s="66" t="s">
         <v>134</v>
@@ -10661,7 +10754,7 @@
         <v>272</v>
       </c>
       <c r="E6" s="62" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F6" s="120" t="s">
         <v>134</v>
@@ -10672,7 +10765,7 @@
         <v>629</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C7" t="s">
         <v>701</v>
@@ -10681,7 +10774,7 @@
         <v>272</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F7" s="120" t="s">
         <v>134</v>
@@ -10701,7 +10794,7 @@
         <v>272</v>
       </c>
       <c r="E8" s="62" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F8" s="120" t="s">
         <v>134</v>
@@ -10759,7 +10852,7 @@
         <v>272</v>
       </c>
       <c r="E11" s="111" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F11" s="120" t="s">
         <v>134</v>
@@ -10767,13 +10860,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
+        <v>762</v>
+      </c>
+      <c r="B12" s="110" t="s">
+        <v>761</v>
+      </c>
+      <c r="C12" s="88" t="s">
         <v>763</v>
-      </c>
-      <c r="B12" s="110" t="s">
-        <v>762</v>
-      </c>
-      <c r="C12" s="88" t="s">
-        <v>764</v>
       </c>
       <c r="D12" s="110" t="s">
         <v>272</v>
@@ -10784,19 +10877,19 @@
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="110" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B13" s="110" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C13" s="88" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D13" s="110" t="s">
         <v>272</v>
       </c>
       <c r="E13" s="62" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F13" s="120" t="s">
         <v>134</v>
@@ -10804,19 +10897,19 @@
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="110" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D14" s="53" t="s">
         <v>272</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F14" s="120" t="s">
         <v>134</v>
@@ -10824,30 +10917,30 @@
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="110" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B15" s="109" t="s">
+        <v>778</v>
+      </c>
+      <c r="C15" s="109" t="s">
         <v>779</v>
-      </c>
-      <c r="C15" s="109" t="s">
-        <v>780</v>
       </c>
       <c r="D15" s="109" t="s">
         <v>272</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F15" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="110" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B16" s="141" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C16" s="88" t="s">
         <v>547</v>
@@ -10861,13 +10954,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="110" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B17" s="141" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C17" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D17" s="141" t="s">
         <v>272</v>
@@ -10878,19 +10971,53 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="110" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B18" s="141" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C18" s="88" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D18" s="141" t="s">
         <v>272</v>
       </c>
       <c r="F18" s="120" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="110" t="s">
+        <v>938</v>
+      </c>
+      <c r="B19" s="141" t="s">
+        <v>939</v>
+      </c>
+      <c r="C19" t="s">
+        <v>940</v>
+      </c>
+      <c r="D19" s="141" t="s">
+        <v>272</v>
+      </c>
+      <c r="F19" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="110" t="s">
+        <v>941</v>
+      </c>
+      <c r="B20" s="141" t="s">
+        <v>942</v>
+      </c>
+      <c r="C20" t="s">
+        <v>944</v>
+      </c>
+      <c r="D20" s="141" t="s">
+        <v>272</v>
+      </c>
+      <c r="F20" s="120" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -10903,6 +11030,118 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="93" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="119" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="119" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1" s="119" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1" s="119" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="119" t="s">
+        <v>606</v>
+      </c>
+      <c r="F1" s="119" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="47" t="s">
+        <v>948</v>
+      </c>
+      <c r="B2" s="82" t="s">
+        <v>946</v>
+      </c>
+      <c r="C2" t="s">
+        <v>947</v>
+      </c>
+      <c r="D2" s="82" t="s">
+        <v>272</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>950</v>
+      </c>
+      <c r="F2" s="66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
+        <v>951</v>
+      </c>
+      <c r="B3" s="82" t="s">
+        <v>952</v>
+      </c>
+      <c r="C3" t="s">
+        <v>953</v>
+      </c>
+      <c r="D3" s="82" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="47"/>
+      <c r="F3" s="66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="47" t="s">
+        <v>954</v>
+      </c>
+      <c r="B4" s="82" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" t="s">
+        <v>955</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" s="47"/>
+      <c r="F4" s="66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="47" t="s">
+        <v>956</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>957</v>
+      </c>
+      <c r="C5" t="s">
+        <v>958</v>
+      </c>
+      <c r="D5" s="82" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="47"/>
+      <c r="F5" s="66" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -13423,7 +13662,7 @@
         <v>93</v>
       </c>
       <c r="B2" s="96" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13439,7 +13678,7 @@
         <v>602</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
@@ -13540,10 +13779,10 @@
     </row>
     <row r="17" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C17" s="66"/>
       <c r="D17" s="66"/>
@@ -29964,7 +30203,7 @@
         <v>633</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="23" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -29980,7 +30219,7 @@
         <v>639</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="25" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -29988,7 +30227,7 @@
         <v>635</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="26" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -30004,7 +30243,7 @@
         <v>656</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="28" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -30012,7 +30251,7 @@
         <v>644</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="29" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -30020,7 +30259,7 @@
         <v>643</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="30" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -30028,7 +30267,7 @@
         <v>645</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="31" spans="1:16384" ht="17.25" x14ac:dyDescent="0.25">
@@ -30093,12 +30332,12 @@
         <v>136</v>
       </c>
       <c r="F1" s="72" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B2" s="121" t="s">
         <v>137</v>
@@ -30118,7 +30357,7 @@
     </row>
     <row r="3" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B3" s="118" t="s">
         <v>312</v>
@@ -30138,7 +30377,7 @@
     </row>
     <row r="4" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B4" s="51" t="s">
         <v>142</v>
@@ -30158,7 +30397,7 @@
     </row>
     <row r="5" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B5" s="118" t="s">
         <v>138</v>
@@ -30178,7 +30417,7 @@
     </row>
     <row r="6" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B6" s="51" t="s">
         <v>309</v>
@@ -30198,7 +30437,7 @@
     </row>
     <row r="7" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B7" s="48" t="s">
         <v>140</v>
@@ -30216,7 +30455,7 @@
     </row>
     <row r="8" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B8" s="51" t="s">
         <v>141</v>
@@ -30234,7 +30473,7 @@
     </row>
     <row r="9" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B9" s="48" t="s">
         <v>139</v>
@@ -30250,7 +30489,7 @@
     </row>
     <row r="10" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>314</v>
@@ -30270,7 +30509,7 @@
     </row>
     <row r="11" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B11" s="48" t="s">
         <v>313</v>
@@ -30427,7 +30666,7 @@
         <v>136</v>
       </c>
       <c r="E1" s="122" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -30688,7 +30927,7 @@
         <v>136</v>
       </c>
       <c r="F1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -30699,7 +30938,7 @@
         <v>319</v>
       </c>
       <c r="C2" s="117" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D2" s="47">
         <v>1</v>
@@ -30719,7 +30958,7 @@
         <v>310</v>
       </c>
       <c r="C3" s="117" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D3" s="47">
         <v>1</v>
@@ -30739,7 +30978,7 @@
         <v>311</v>
       </c>
       <c r="C4" s="117" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D4" s="47">
         <v>0</v>
@@ -30759,7 +30998,7 @@
         <v>148</v>
       </c>
       <c r="C5" s="117" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D5" s="47">
         <v>1</v>
@@ -31146,7 +31385,7 @@
         <v>136</v>
       </c>
       <c r="X1" s="124" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -31154,10 +31393,10 @@
         <v>205</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D2" s="30">
         <v>46226</v>
@@ -31179,13 +31418,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N2" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="O2" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O2" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P2" s="12" t="s">
         <v>39</v>
@@ -31220,10 +31459,10 @@
         <v>206</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D3" s="30">
         <v>46226</v>
@@ -31235,7 +31474,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H3" s="30">
         <v>46242</v>
@@ -31249,13 +31488,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N3" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N3" s="44" t="s">
+      <c r="O3" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O3" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>39</v>
@@ -31290,10 +31529,10 @@
         <v>207</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D4" s="30">
         <v>46226</v>
@@ -31305,13 +31544,13 @@
         <v>390</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H4" s="30">
         <v>46248</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13">
@@ -31321,13 +31560,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N4" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N4" s="44" t="s">
+      <c r="O4" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O4" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>39</v>
@@ -31362,10 +31601,10 @@
         <v>208</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D5" s="30">
         <v>46226</v>
@@ -31377,7 +31616,7 @@
         <v>391</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H5" s="30">
         <v>46264</v>
@@ -31393,13 +31632,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N5" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N5" s="44" t="s">
+      <c r="O5" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O5" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>39</v>
@@ -31434,10 +31673,10 @@
         <v>209</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D6" s="30">
         <v>46226</v>
@@ -31449,7 +31688,7 @@
         <v>392</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H6" s="30">
         <v>46264</v>
@@ -31465,13 +31704,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N6" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N6" s="44" t="s">
+      <c r="O6" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O6" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P6" s="12" t="s">
         <v>39</v>
@@ -31506,10 +31745,10 @@
         <v>210</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D7" s="30">
         <v>46226</v>
@@ -31521,7 +31760,7 @@
         <v>395</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H7" s="30">
         <v>46417</v>
@@ -31537,13 +31776,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N7" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N7" s="44" t="s">
+      <c r="O7" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O7" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P7" s="12" t="s">
         <v>39</v>
@@ -31578,10 +31817,10 @@
         <v>211</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D8" s="30">
         <v>46226</v>
@@ -31593,7 +31832,7 @@
         <v>393</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H8" s="30">
         <v>46537</v>
@@ -31609,13 +31848,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N8" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N8" s="44" t="s">
+      <c r="O8" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O8" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P8" s="12" t="s">
         <v>39</v>
@@ -31650,10 +31889,10 @@
         <v>212</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D9" s="30">
         <v>46226</v>
@@ -31665,7 +31904,7 @@
         <v>397</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H9" s="30">
         <v>46264</v>
@@ -31681,13 +31920,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N9" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N9" s="44" t="s">
+      <c r="O9" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O9" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>39</v>
@@ -33821,7 +34060,7 @@
     </row>
     <row r="51" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="48" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B51" s="56" t="s">
         <v>394</v>
@@ -33863,7 +34102,7 @@
     </row>
     <row r="52" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="48" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B52" s="56" t="s">
         <v>331</v>
@@ -33905,7 +34144,7 @@
     </row>
     <row r="53" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="48" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B53" s="56" t="s">
         <v>396</v>
@@ -33947,7 +34186,7 @@
     </row>
     <row r="54" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="48" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B54" s="56" t="s">
         <v>332</v>
@@ -33989,7 +34228,7 @@
     </row>
     <row r="55" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="48" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B55" s="56" t="s">
         <v>333</v>
@@ -34033,7 +34272,7 @@
     </row>
     <row r="56" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="48" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B56" s="56" t="s">
         <v>334</v>
@@ -34075,7 +34314,7 @@
     </row>
     <row r="57" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="48" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B57" s="56" t="s">
         <v>335</v>
@@ -34117,7 +34356,7 @@
     </row>
     <row r="58" spans="1:24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="48" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B58" s="56" t="s">
         <v>336</v>
@@ -34916,7 +35155,7 @@
         <v>136</v>
       </c>
       <c r="Y1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -34927,7 +35166,7 @@
         <v>150</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D2" s="30">
         <v>46226</v>
@@ -34949,13 +35188,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N2" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="O2" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O2" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P2" s="47" t="s">
         <v>39</v>
@@ -34964,7 +35203,7 @@
         <v>28</v>
       </c>
       <c r="R2" s="47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S2" s="47" t="s">
         <v>29</v>
@@ -34993,10 +35232,10 @@
         <v>238</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D3" s="30">
         <v>46211</v>
@@ -35008,7 +35247,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H3" s="30">
         <v>46242</v>
@@ -35022,13 +35261,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N3" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N3" s="44" t="s">
+      <c r="O3" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O3" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P3" s="47" t="s">
         <v>39</v>
@@ -35037,7 +35276,7 @@
         <v>28</v>
       </c>
       <c r="R3" s="47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S3" s="47" t="s">
         <v>29</v>
@@ -35066,10 +35305,10 @@
         <v>239</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D4" s="30">
         <v>46211</v>
@@ -35081,13 +35320,13 @@
         <v>390</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H4" s="30">
         <v>46248</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13">
@@ -35097,13 +35336,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N4" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N4" s="44" t="s">
+      <c r="O4" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O4" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P4" s="47" t="s">
         <v>39</v>
@@ -35112,7 +35351,7 @@
         <v>28</v>
       </c>
       <c r="R4" s="47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S4" s="47" t="s">
         <v>29</v>
@@ -35141,10 +35380,10 @@
         <v>240</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D5" s="30">
         <v>46211</v>
@@ -35156,7 +35395,7 @@
         <v>391</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H5" s="30">
         <v>46264</v>
@@ -35172,13 +35411,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N5" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N5" s="44" t="s">
+      <c r="O5" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O5" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P5" s="47" t="s">
         <v>39</v>
@@ -35187,7 +35426,7 @@
         <v>28</v>
       </c>
       <c r="R5" s="47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S5" s="47" t="s">
         <v>29</v>
@@ -35216,10 +35455,10 @@
         <v>241</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D6" s="30">
         <v>46211</v>
@@ -35231,7 +35470,7 @@
         <v>392</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H6" s="30">
         <v>46264</v>
@@ -35247,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N6" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N6" s="44" t="s">
+      <c r="O6" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O6" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P6" s="47" t="s">
         <v>39</v>
@@ -35262,7 +35501,7 @@
         <v>28</v>
       </c>
       <c r="R6" s="47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S6" s="47" t="s">
         <v>29</v>
@@ -35291,10 +35530,10 @@
         <v>242</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D7" s="30">
         <v>46211</v>
@@ -35306,7 +35545,7 @@
         <v>395</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H7" s="30">
         <v>46417</v>
@@ -35322,13 +35561,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N7" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N7" s="44" t="s">
+      <c r="O7" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O7" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P7" s="47" t="s">
         <v>39</v>
@@ -35337,7 +35576,7 @@
         <v>28</v>
       </c>
       <c r="R7" s="47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S7" s="47" t="s">
         <v>29</v>
@@ -35366,10 +35605,10 @@
         <v>243</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D8" s="30">
         <v>46211</v>
@@ -35381,7 +35620,7 @@
         <v>393</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H8" s="30">
         <v>46537</v>
@@ -35397,13 +35636,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N8" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N8" s="44" t="s">
+      <c r="O8" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O8" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P8" s="47" t="s">
         <v>39</v>
@@ -35412,7 +35651,7 @@
         <v>28</v>
       </c>
       <c r="R8" s="47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S8" s="47" t="s">
         <v>29</v>
@@ -35441,10 +35680,10 @@
         <v>244</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D9" s="30">
         <v>46211</v>
@@ -35456,7 +35695,7 @@
         <v>397</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H9" s="30">
         <v>46233</v>
@@ -35472,13 +35711,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="44" t="s">
+        <v>840</v>
+      </c>
+      <c r="N9" s="44" t="s">
         <v>841</v>
       </c>
-      <c r="N9" s="44" t="s">
+      <c r="O9" s="44" t="s">
         <v>842</v>
-      </c>
-      <c r="O9" s="44" t="s">
-        <v>843</v>
       </c>
       <c r="P9" s="47" t="s">
         <v>39</v>
@@ -35487,7 +35726,7 @@
         <v>28</v>
       </c>
       <c r="R9" s="47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S9" s="47" t="s">
         <v>29</v>
@@ -37763,7 +38002,7 @@
     </row>
     <row r="52" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="47" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B52" s="47" t="s">
         <v>330</v>
@@ -37808,7 +38047,7 @@
     </row>
     <row r="53" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="47" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B53" s="78" t="s">
         <v>331</v>
@@ -37853,7 +38092,7 @@
     </row>
     <row r="54" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="47" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B54" s="47" t="s">
         <v>332</v>
@@ -37900,7 +38139,7 @@
     </row>
     <row r="55" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="47" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B55" s="78" t="s">
         <v>333</v>
@@ -37945,7 +38184,7 @@
     </row>
     <row r="56" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="47" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B56" s="47" t="s">
         <v>334</v>
@@ -37990,7 +38229,7 @@
     </row>
     <row r="57" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="47" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B57" s="78" t="s">
         <v>335</v>
@@ -38035,7 +38274,7 @@
     </row>
     <row r="58" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="47" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B58" s="47" t="s">
         <v>336</v>
@@ -39102,18 +39341,18 @@
         <v>136</v>
       </c>
       <c r="E1" s="119" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="2" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
+        <v>785</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>786</v>
       </c>
-      <c r="B2" s="47" t="s">
-        <v>787</v>
-      </c>
       <c r="C2" s="62" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>272</v>
@@ -39124,13 +39363,13 @@
     </row>
     <row r="3" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C3" s="62" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>272</v>
@@ -39141,13 +39380,13 @@
     </row>
     <row r="4" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C4" s="62" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>272</v>
@@ -39158,13 +39397,13 @@
     </row>
     <row r="5" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>272</v>
@@ -39175,13 +39414,13 @@
     </row>
     <row r="6" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>272</v>
@@ -39192,13 +39431,13 @@
     </row>
     <row r="7" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C7" s="62" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>272</v>
@@ -39209,13 +39448,13 @@
     </row>
     <row r="8" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>272</v>
@@ -39226,13 +39465,13 @@
     </row>
     <row r="9" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>272</v>
@@ -39243,13 +39482,13 @@
     </row>
     <row r="10" spans="1:5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C10" s="62" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D10" s="47" t="s">
         <v>272</v>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2891" uniqueCount="962">
   <si>
     <t>task_name</t>
   </si>
@@ -2934,6 +2934,15 @@
   </si>
   <si>
     <t>verify search company name  data details</t>
+  </si>
+  <si>
+    <t>view_column_headers</t>
+  </si>
+  <si>
+    <t>TC_Audit_5</t>
+  </si>
+  <si>
+    <t>Verify View Column Headers</t>
   </si>
 </sst>
 </file>
@@ -11031,7 +11040,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11133,11 +11142,29 @@
       </c>
       <c r="E5" s="47"/>
       <c r="F5" s="66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="47" t="s">
+        <v>960</v>
+      </c>
+      <c r="B6" s="120" t="s">
+        <v>959</v>
+      </c>
+      <c r="C6" t="s">
+        <v>961</v>
+      </c>
+      <c r="D6" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="120" t="s">
         <v>133</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2891" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2901" uniqueCount="968">
   <si>
     <t>task_name</t>
   </si>
@@ -2943,6 +2943,24 @@
   </si>
   <si>
     <t>Verify View Column Headers</t>
+  </si>
+  <si>
+    <t>TC_Audit_6</t>
+  </si>
+  <si>
+    <t>create_template</t>
+  </si>
+  <si>
+    <t>Verify create template</t>
+  </si>
+  <si>
+    <t>TC_Audit_7</t>
+  </si>
+  <si>
+    <t>search_template_name</t>
+  </si>
+  <si>
+    <t>Verify search template name data details</t>
   </si>
 </sst>
 </file>
@@ -11040,7 +11058,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11159,6 +11177,40 @@
         <v>272</v>
       </c>
       <c r="F6" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>962</v>
+      </c>
+      <c r="B7" s="120" t="s">
+        <v>963</v>
+      </c>
+      <c r="C7" t="s">
+        <v>964</v>
+      </c>
+      <c r="D7" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="47" t="s">
+        <v>965</v>
+      </c>
+      <c r="B8" s="120" t="s">
+        <v>966</v>
+      </c>
+      <c r="C8" t="s">
+        <v>967</v>
+      </c>
+      <c r="D8" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="120" t="s">
         <v>133</v>
       </c>
     </row>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2901" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="975">
   <si>
     <t>task_name</t>
   </si>
@@ -2961,6 +2961,27 @@
   </si>
   <si>
     <t>Verify search template name data details</t>
+  </si>
+  <si>
+    <t>TC_Audit_8</t>
+  </si>
+  <si>
+    <t>custom_export_data</t>
+  </si>
+  <si>
+    <t>TC_Audit_9</t>
+  </si>
+  <si>
+    <t>custom_view_column_headers</t>
+  </si>
+  <si>
+    <t>TC_Audit_10</t>
+  </si>
+  <si>
+    <t>create_assignment</t>
+  </si>
+  <si>
+    <t>Verify Assignment</t>
   </si>
 </sst>
 </file>
@@ -11058,7 +11079,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11211,6 +11232,57 @@
         <v>272</v>
       </c>
       <c r="F8" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="47" t="s">
+        <v>968</v>
+      </c>
+      <c r="B9" s="120" t="s">
+        <v>969</v>
+      </c>
+      <c r="C9" t="s">
+        <v>955</v>
+      </c>
+      <c r="D9" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="47" t="s">
+        <v>970</v>
+      </c>
+      <c r="B10" s="120" t="s">
+        <v>971</v>
+      </c>
+      <c r="C10" t="s">
+        <v>961</v>
+      </c>
+      <c r="D10" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F10" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="47" t="s">
+        <v>972</v>
+      </c>
+      <c r="B11" s="120" t="s">
+        <v>973</v>
+      </c>
+      <c r="C11" t="s">
+        <v>974</v>
+      </c>
+      <c r="D11" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F11" s="120" t="s">
         <v>133</v>
       </c>
     </row>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -2906,9 +2906,6 @@
     <t>TC_Audit_1</t>
   </si>
   <si>
-    <t>bhavani+69@secmark.in</t>
-  </si>
-  <si>
     <t>{"email_id" : "testuser234@gmail.com"}</t>
   </si>
   <si>
@@ -2982,6 +2979,9 @@
   </si>
   <si>
     <t>Verify Assignment</t>
+  </si>
+  <si>
+    <t>bhavani+71@secmark.in</t>
   </si>
 </sst>
 </file>
@@ -6639,7 +6639,7 @@
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>949</v>
+        <v>974</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>339</v>
@@ -11124,21 +11124,21 @@
         <v>272</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
+        <v>950</v>
+      </c>
+      <c r="B3" s="82" t="s">
         <v>951</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="C3" t="s">
         <v>952</v>
-      </c>
-      <c r="C3" t="s">
-        <v>953</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>272</v>
@@ -11150,13 +11150,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B4" s="82" t="s">
         <v>293</v>
       </c>
       <c r="C4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D4" s="82" t="s">
         <v>272</v>
@@ -11168,13 +11168,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
+        <v>955</v>
+      </c>
+      <c r="B5" s="82" t="s">
         <v>956</v>
       </c>
-      <c r="B5" s="82" t="s">
+      <c r="C5" t="s">
         <v>957</v>
-      </c>
-      <c r="C5" t="s">
-        <v>958</v>
       </c>
       <c r="D5" s="82" t="s">
         <v>272</v>
@@ -11186,13 +11186,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
+        <v>959</v>
+      </c>
+      <c r="B6" s="120" t="s">
+        <v>958</v>
+      </c>
+      <c r="C6" t="s">
         <v>960</v>
-      </c>
-      <c r="B6" s="120" t="s">
-        <v>959</v>
-      </c>
-      <c r="C6" t="s">
-        <v>961</v>
       </c>
       <c r="D6" s="120" t="s">
         <v>272</v>
@@ -11203,13 +11203,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
+        <v>961</v>
+      </c>
+      <c r="B7" s="120" t="s">
         <v>962</v>
       </c>
-      <c r="B7" s="120" t="s">
+      <c r="C7" t="s">
         <v>963</v>
-      </c>
-      <c r="C7" t="s">
-        <v>964</v>
       </c>
       <c r="D7" s="120" t="s">
         <v>272</v>
@@ -11220,13 +11220,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
+        <v>964</v>
+      </c>
+      <c r="B8" s="120" t="s">
         <v>965</v>
       </c>
-      <c r="B8" s="120" t="s">
+      <c r="C8" t="s">
         <v>966</v>
-      </c>
-      <c r="C8" t="s">
-        <v>967</v>
       </c>
       <c r="D8" s="120" t="s">
         <v>272</v>
@@ -11237,13 +11237,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
+        <v>967</v>
+      </c>
+      <c r="B9" s="120" t="s">
         <v>968</v>
       </c>
-      <c r="B9" s="120" t="s">
-        <v>969</v>
-      </c>
       <c r="C9" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D9" s="120" t="s">
         <v>272</v>
@@ -11254,13 +11254,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
+        <v>969</v>
+      </c>
+      <c r="B10" s="120" t="s">
         <v>970</v>
       </c>
-      <c r="B10" s="120" t="s">
-        <v>971</v>
-      </c>
       <c r="C10" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D10" s="120" t="s">
         <v>272</v>
@@ -11271,19 +11271,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
+        <v>971</v>
+      </c>
+      <c r="B11" s="120" t="s">
         <v>972</v>
       </c>
-      <c r="B11" s="120" t="s">
+      <c r="C11" t="s">
         <v>973</v>
-      </c>
-      <c r="C11" t="s">
-        <v>974</v>
       </c>
       <c r="D11" s="120" t="s">
         <v>272</v>
       </c>
       <c r="F11" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2916" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="978">
   <si>
     <t>task_name</t>
   </si>
@@ -2981,7 +2981,16 @@
     <t>Verify Assignment</t>
   </si>
   <si>
-    <t>bhavani+71@secmark.in</t>
+    <t>TC_Audit_11</t>
+  </si>
+  <si>
+    <t>Verify Company</t>
+  </si>
+  <si>
+    <t>edit_company_name</t>
+  </si>
+  <si>
+    <t>bhavani+70@secmark.in</t>
   </si>
 </sst>
 </file>
@@ -6639,7 +6648,7 @@
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>339</v>
@@ -11079,7 +11088,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11145,7 +11154,7 @@
       </c>
       <c r="E3" s="47"/>
       <c r="F3" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -11283,6 +11292,23 @@
         <v>272</v>
       </c>
       <c r="F11" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="47" t="s">
+        <v>974</v>
+      </c>
+      <c r="B12" s="120" t="s">
+        <v>976</v>
+      </c>
+      <c r="C12" t="s">
+        <v>975</v>
+      </c>
+      <c r="D12" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F12" s="120" t="s">
         <v>134</v>
       </c>
     </row>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="981">
   <si>
     <t>task_name</t>
   </si>
@@ -2900,9 +2900,6 @@
     <t>audit_company</t>
   </si>
   <si>
-    <t>verify audit company details</t>
-  </si>
-  <si>
     <t>TC_Audit_1</t>
   </si>
   <si>
@@ -2915,9 +2912,6 @@
     <t>audit_branch</t>
   </si>
   <si>
-    <t>verify audit branch details</t>
-  </si>
-  <si>
     <t>TC_Audit_3</t>
   </si>
   <si>
@@ -2991,6 +2985,21 @@
   </si>
   <si>
     <t>bhavani+70@secmark.in</t>
+  </si>
+  <si>
+    <t>edit_inside_template</t>
+  </si>
+  <si>
+    <t>TC_Audit_12</t>
+  </si>
+  <si>
+    <t>Verify Edit Template</t>
+  </si>
+  <si>
+    <t>Verify that all company details entered during company creation</t>
+  </si>
+  <si>
+    <t>Verify that all branch details are correctly entered, saved, and displayed after creating an audit branch.</t>
   </si>
 </sst>
 </file>
@@ -6648,7 +6657,7 @@
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>339</v>
@@ -11088,7 +11097,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11121,51 +11130,51 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B2" s="82" t="s">
         <v>946</v>
       </c>
       <c r="C2" t="s">
-        <v>947</v>
+        <v>979</v>
       </c>
       <c r="D2" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
+        <v>949</v>
+      </c>
+      <c r="B3" s="82" t="s">
         <v>950</v>
       </c>
-      <c r="B3" s="82" t="s">
-        <v>951</v>
-      </c>
       <c r="C3" t="s">
-        <v>952</v>
+        <v>980</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E3" s="47"/>
       <c r="F3" s="66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B4" s="82" t="s">
         <v>293</v>
       </c>
       <c r="C4" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D4" s="82" t="s">
         <v>272</v>
@@ -11177,13 +11186,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
+        <v>953</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>954</v>
+      </c>
+      <c r="C5" t="s">
         <v>955</v>
-      </c>
-      <c r="B5" s="82" t="s">
-        <v>956</v>
-      </c>
-      <c r="C5" t="s">
-        <v>957</v>
       </c>
       <c r="D5" s="82" t="s">
         <v>272</v>
@@ -11195,13 +11204,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B6" s="120" t="s">
+        <v>956</v>
+      </c>
+      <c r="C6" t="s">
         <v>958</v>
-      </c>
-      <c r="C6" t="s">
-        <v>960</v>
       </c>
       <c r="D6" s="120" t="s">
         <v>272</v>
@@ -11212,13 +11221,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
+        <v>959</v>
+      </c>
+      <c r="B7" s="120" t="s">
+        <v>960</v>
+      </c>
+      <c r="C7" t="s">
         <v>961</v>
-      </c>
-      <c r="B7" s="120" t="s">
-        <v>962</v>
-      </c>
-      <c r="C7" t="s">
-        <v>963</v>
       </c>
       <c r="D7" s="120" t="s">
         <v>272</v>
@@ -11229,13 +11238,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
+        <v>962</v>
+      </c>
+      <c r="B8" s="120" t="s">
+        <v>963</v>
+      </c>
+      <c r="C8" t="s">
         <v>964</v>
-      </c>
-      <c r="B8" s="120" t="s">
-        <v>965</v>
-      </c>
-      <c r="C8" t="s">
-        <v>966</v>
       </c>
       <c r="D8" s="120" t="s">
         <v>272</v>
@@ -11246,13 +11255,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B9" s="120" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C9" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D9" s="120" t="s">
         <v>272</v>
@@ -11263,13 +11272,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B10" s="120" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C10" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D10" s="120" t="s">
         <v>272</v>
@@ -11280,13 +11289,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
+        <v>969</v>
+      </c>
+      <c r="B11" s="120" t="s">
+        <v>970</v>
+      </c>
+      <c r="C11" t="s">
         <v>971</v>
-      </c>
-      <c r="B11" s="120" t="s">
-        <v>972</v>
-      </c>
-      <c r="C11" t="s">
-        <v>973</v>
       </c>
       <c r="D11" s="120" t="s">
         <v>272</v>
@@ -11297,19 +11306,36 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
+        <v>972</v>
+      </c>
+      <c r="B12" s="120" t="s">
         <v>974</v>
       </c>
-      <c r="B12" s="120" t="s">
-        <v>976</v>
-      </c>
       <c r="C12" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D12" s="120" t="s">
         <v>272</v>
       </c>
       <c r="F12" s="120" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="47" t="s">
+        <v>977</v>
+      </c>
+      <c r="B13" s="120" t="s">
+        <v>976</v>
+      </c>
+      <c r="C13" t="s">
+        <v>978</v>
+      </c>
+      <c r="D13" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F13" s="120" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2931" uniqueCount="986">
   <si>
     <t>task_name</t>
   </si>
@@ -2915,45 +2915,30 @@
     <t>TC_Audit_3</t>
   </si>
   <si>
-    <t>verify Export data details</t>
-  </si>
-  <si>
     <t>TC_Audit_4</t>
   </si>
   <si>
     <t>search_company_name</t>
   </si>
   <si>
-    <t>verify search company name  data details</t>
-  </si>
-  <si>
     <t>view_column_headers</t>
   </si>
   <si>
     <t>TC_Audit_5</t>
   </si>
   <si>
-    <t>Verify View Column Headers</t>
-  </si>
-  <si>
     <t>TC_Audit_6</t>
   </si>
   <si>
     <t>create_template</t>
   </si>
   <si>
-    <t>Verify create template</t>
-  </si>
-  <si>
     <t>TC_Audit_7</t>
   </si>
   <si>
     <t>search_template_name</t>
   </si>
   <si>
-    <t>Verify search template name data details</t>
-  </si>
-  <si>
     <t>TC_Audit_8</t>
   </si>
   <si>
@@ -2972,15 +2957,9 @@
     <t>create_assignment</t>
   </si>
   <si>
-    <t>Verify Assignment</t>
-  </si>
-  <si>
     <t>TC_Audit_11</t>
   </si>
   <si>
-    <t>Verify Company</t>
-  </si>
-  <si>
     <t>edit_company_name</t>
   </si>
   <si>
@@ -2993,13 +2972,49 @@
     <t>TC_Audit_12</t>
   </si>
   <si>
-    <t>Verify Edit Template</t>
-  </si>
-  <si>
     <t>Verify that all company details entered during company creation</t>
   </si>
   <si>
     <t>Verify that all branch details are correctly entered, saved, and displayed after creating an audit branch.</t>
+  </si>
+  <si>
+    <t>Verify that the company can be searched successfully using its name.</t>
+  </si>
+  <si>
+    <t>Verify that the selected and deselected columns are correctly displayed in the column headers.</t>
+  </si>
+  <si>
+    <t>Verify that a template can be created successfully with all the required details.</t>
+  </si>
+  <si>
+    <t>Verify that the template can be searched successfully using its name.</t>
+  </si>
+  <si>
+    <t>Verify that the company data is exported successfully</t>
+  </si>
+  <si>
+    <t>Verify that the custom template data is exported successfully</t>
+  </si>
+  <si>
+    <t>Verify that an assignment can be created successfully with all required details</t>
+  </si>
+  <si>
+    <t>Verify that company details can be edited and updated successfully</t>
+  </si>
+  <si>
+    <t>Verify that a template can be edited and updated successfully</t>
+  </si>
+  <si>
+    <t>company_export_data</t>
+  </si>
+  <si>
+    <t>TC_Audit_13</t>
+  </si>
+  <si>
+    <t>add_questionnaire</t>
+  </si>
+  <si>
+    <t>Verify that all questionnaire can be created successfully with all required details</t>
   </si>
 </sst>
 </file>
@@ -6657,7 +6672,7 @@
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>339</v>
@@ -11097,7 +11112,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11136,7 +11151,7 @@
         <v>946</v>
       </c>
       <c r="C2" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D2" s="82" t="s">
         <v>272</v>
@@ -11156,7 +11171,7 @@
         <v>950</v>
       </c>
       <c r="C3" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>272</v>
@@ -11171,10 +11186,10 @@
         <v>951</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>293</v>
+        <v>982</v>
       </c>
       <c r="C4" t="s">
-        <v>952</v>
+        <v>977</v>
       </c>
       <c r="D4" s="82" t="s">
         <v>272</v>
@@ -11186,13 +11201,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
+        <v>952</v>
+      </c>
+      <c r="B5" s="82" t="s">
         <v>953</v>
       </c>
-      <c r="B5" s="82" t="s">
-        <v>954</v>
-      </c>
       <c r="C5" t="s">
-        <v>955</v>
+        <v>973</v>
       </c>
       <c r="D5" s="82" t="s">
         <v>272</v>
@@ -11204,13 +11219,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B6" s="120" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C6" t="s">
-        <v>958</v>
+        <v>974</v>
       </c>
       <c r="D6" s="120" t="s">
         <v>272</v>
@@ -11221,13 +11236,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B7" s="120" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C7" t="s">
-        <v>961</v>
+        <v>975</v>
       </c>
       <c r="D7" s="120" t="s">
         <v>272</v>
@@ -11238,13 +11253,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B8" s="120" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C8" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D8" s="120" t="s">
         <v>272</v>
@@ -11255,13 +11270,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="B9" s="120" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="C9" t="s">
-        <v>952</v>
+        <v>978</v>
       </c>
       <c r="D9" s="120" t="s">
         <v>272</v>
@@ -11272,13 +11287,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="B10" s="120" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="C10" t="s">
-        <v>958</v>
+        <v>974</v>
       </c>
       <c r="D10" s="120" t="s">
         <v>272</v>
@@ -11289,13 +11304,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="B11" s="120" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="C11" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="D11" s="120" t="s">
         <v>272</v>
@@ -11306,13 +11321,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="B12" s="120" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="C12" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="D12" s="120" t="s">
         <v>272</v>
@@ -11323,18 +11338,35 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="B13" s="120" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="C13" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D13" s="120" t="s">
         <v>272</v>
       </c>
       <c r="F13" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
+        <v>983</v>
+      </c>
+      <c r="B14" s="120" t="s">
+        <v>984</v>
+      </c>
+      <c r="C14" t="s">
+        <v>985</v>
+      </c>
+      <c r="D14" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F14" s="120" t="s">
         <v>133</v>
       </c>
     </row>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2931" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="989">
   <si>
     <t>task_name</t>
   </si>
@@ -3015,6 +3015,15 @@
   </si>
   <si>
     <t>Verify that all questionnaire can be created successfully with all required details</t>
+  </si>
+  <si>
+    <t>TC_Audit_14</t>
+  </si>
+  <si>
+    <t>add_checklist</t>
+  </si>
+  <si>
+    <t>Verify that Checklist can be created successfully with all required details</t>
   </si>
 </sst>
 </file>
@@ -11112,7 +11121,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11367,6 +11376,23 @@
         <v>272</v>
       </c>
       <c r="F14" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="115" t="s">
+        <v>986</v>
+      </c>
+      <c r="B15" s="120" t="s">
+        <v>987</v>
+      </c>
+      <c r="C15" t="s">
+        <v>988</v>
+      </c>
+      <c r="D15" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="F15" s="120" t="s">
         <v>133</v>
       </c>
     </row>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -11376,7 +11376,7 @@
         <v>272</v>
       </c>
       <c r="F14" s="120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="993">
   <si>
     <t>task_name</t>
   </si>
@@ -3024,6 +3024,18 @@
   </si>
   <si>
     <t>Verify that Checklist can be created successfully with all required details</t>
+  </si>
+  <si>
+    <t>TC_Audit_15</t>
+  </si>
+  <si>
+    <t>Verify that Assign Questionnaire to Sub Auditee</t>
+  </si>
+  <si>
+    <t>{"email_id" : "bhavani+89@secmark.in"}</t>
+  </si>
+  <si>
+    <t>add_assign_form</t>
   </si>
 </sst>
 </file>
@@ -11121,7 +11133,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11376,7 +11388,7 @@
         <v>272</v>
       </c>
       <c r="F14" s="120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -11393,6 +11405,26 @@
         <v>272</v>
       </c>
       <c r="F15" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="115" t="s">
+        <v>989</v>
+      </c>
+      <c r="B16" s="120" t="s">
+        <v>992</v>
+      </c>
+      <c r="C16" t="s">
+        <v>990</v>
+      </c>
+      <c r="D16" s="120" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>991</v>
+      </c>
+      <c r="F16" s="120" t="s">
         <v>133</v>
       </c>
     </row>

--- a/data/test_case_selector.xlsx
+++ b/data/test_case_selector.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2943" uniqueCount="993">
   <si>
     <t>task_name</t>
   </si>
@@ -2903,9 +2903,6 @@
     <t>TC_Audit_1</t>
   </si>
   <si>
-    <t>{"email_id" : "testuser234@gmail.com"}</t>
-  </si>
-  <si>
     <t>TC_Audit_2</t>
   </si>
   <si>
@@ -3032,10 +3029,13 @@
     <t>Verify that Assign Questionnaire to Sub Auditee</t>
   </si>
   <si>
-    <t>{"email_id" : "bhavani+89@secmark.in"}</t>
-  </si>
-  <si>
     <t>add_assign_form</t>
+  </si>
+  <si>
+    <t>{"email_id" : "bhavani+69@secmark.in"}</t>
+  </si>
+  <si>
+    <t>{"head_of_auditor":"bhavani+69@secmark.in"}</t>
   </si>
 </sst>
 </file>
@@ -6693,7 +6693,7 @@
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>339</v>
@@ -11172,13 +11172,13 @@
         <v>946</v>
       </c>
       <c r="C2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D2" s="82" t="s">
         <v>272</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>948</v>
+        <v>991</v>
       </c>
       <c r="F2" s="66" t="s">
         <v>134</v>
@@ -11186,13 +11186,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
+        <v>948</v>
+      </c>
+      <c r="B3" s="82" t="s">
         <v>949</v>
       </c>
-      <c r="B3" s="82" t="s">
-        <v>950</v>
-      </c>
       <c r="C3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>272</v>
@@ -11204,13 +11204,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D4" s="82" t="s">
         <v>272</v>
@@ -11222,13 +11222,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
+        <v>951</v>
+      </c>
+      <c r="B5" s="82" t="s">
         <v>952</v>
       </c>
-      <c r="B5" s="82" t="s">
-        <v>953</v>
-      </c>
       <c r="C5" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D5" s="82" t="s">
         <v>272</v>
@@ -11240,13 +11240,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B6" s="120" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C6" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D6" s="120" t="s">
         <v>272</v>
@@ -11257,13 +11257,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="47" t="s">
+        <v>955</v>
+      </c>
+      <c r="B7" s="120" t="s">
         <v>956</v>
       </c>
-      <c r="B7" s="120" t="s">
-        <v>957</v>
-      </c>
       <c r="C7" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D7" s="120" t="s">
         <v>272</v>
@@ -11274,13 +11274,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
+        <v>957</v>
+      </c>
+      <c r="B8" s="120" t="s">
         <v>958</v>
       </c>
-      <c r="B8" s="120" t="s">
-        <v>959</v>
-      </c>
       <c r="C8" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D8" s="120" t="s">
         <v>272</v>
@@ -11291,13 +11291,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
+        <v>959</v>
+      </c>
+      <c r="B9" s="120" t="s">
         <v>960</v>
       </c>
-      <c r="B9" s="120" t="s">
-        <v>961</v>
-      </c>
       <c r="C9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D9" s="120" t="s">
         <v>272</v>
@@ -11308,13 +11308,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
+        <v>961</v>
+      </c>
+      <c r="B10" s="120" t="s">
         <v>962</v>
       </c>
-      <c r="B10" s="120" t="s">
-        <v>963</v>
-      </c>
       <c r="C10" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D10" s="120" t="s">
         <v>272</v>
@@ -11325,30 +11325,33 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
+        <v>963</v>
+      </c>
+      <c r="B11" s="120" t="s">
         <v>964</v>
       </c>
-      <c r="B11" s="120" t="s">
-        <v>965</v>
-      </c>
       <c r="C11" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D11" s="120" t="s">
         <v>272</v>
       </c>
+      <c r="E11" t="s">
+        <v>992</v>
+      </c>
       <c r="F11" s="120" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
+        <v>965</v>
+      </c>
+      <c r="B12" s="120" t="s">
         <v>966</v>
       </c>
-      <c r="B12" s="120" t="s">
-        <v>967</v>
-      </c>
       <c r="C12" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D12" s="120" t="s">
         <v>272</v>
@@ -11359,13 +11362,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B13" s="120" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C13" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="D13" s="120" t="s">
         <v>272</v>
@@ -11376,13 +11379,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
+        <v>982</v>
+      </c>
+      <c r="B14" s="120" t="s">
         <v>983</v>
       </c>
-      <c r="B14" s="120" t="s">
+      <c r="C14" t="s">
         <v>984</v>
-      </c>
-      <c r="C14" t="s">
-        <v>985</v>
       </c>
       <c r="D14" s="120" t="s">
         <v>272</v>
@@ -11393,13 +11396,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="115" t="s">
+        <v>985</v>
+      </c>
+      <c r="B15" s="120" t="s">
         <v>986</v>
       </c>
-      <c r="B15" s="120" t="s">
+      <c r="C15" t="s">
         <v>987</v>
-      </c>
-      <c r="C15" t="s">
-        <v>988</v>
       </c>
       <c r="D15" s="120" t="s">
         <v>272</v>
@@ -11410,13 +11413,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="115" t="s">
+        <v>988</v>
+      </c>
+      <c r="B16" s="120" t="s">
+        <v>990</v>
+      </c>
+      <c r="C16" t="s">
         <v>989</v>
-      </c>
-      <c r="B16" s="120" t="s">
-        <v>992</v>
-      </c>
-      <c r="C16" t="s">
-        <v>990</v>
       </c>
       <c r="D16" s="120" t="s">
         <v>272</v>
